--- a/MentorPodSorting.xlsx
+++ b/MentorPodSorting.xlsx
@@ -494,22 +494,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lila</t>
+          <t>Edda</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Granados</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Business Solutions Project (PMBS)</t>
+          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -556,22 +556,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lila</t>
+          <t>Edda</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Granados</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Business Solutions Project (PMBS)</t>
+          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -582,32 +582,32 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Lian</t>
+          <t>Priya</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Callahan</t>
+          <t>Balakrishnan</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>lian.callahan@warriorlife.net</t>
+          <t>priya.balakrishnan@warriorlife.net</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>9/10/2025 15:11:54</t>
+          <t>9/12/2025 6:40:22</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -618,22 +618,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lila</t>
+          <t>Edda</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Granados</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Business Solutions Project (PMBS)</t>
+          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -649,12 +649,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Jian</t>
+          <t>Lian</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>Callahan</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -664,12 +664,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>jian.jensen@warriorlife.net</t>
+          <t>lian.callahan@warriorlife.net</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>9/10/2025 15:11:02</t>
+          <t>9/10/2025 15:11:54</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -680,22 +680,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lila</t>
+          <t>Edda</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Granados</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Business Solutions Project (PMBS)</t>
+          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -711,12 +711,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Angelo</t>
+          <t>Jian</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Khatri</t>
+          <t>Jensen</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -726,12 +726,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>angelo.khatri@warriorlife.net</t>
+          <t>jian.jensen@warriorlife.net</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>9/11/2025 22:19:08</t>
+          <t>9/10/2025 15:11:02</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -742,22 +742,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lila</t>
+          <t>Edda</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Granados</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Business Solutions Project (PMBS)</t>
+          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -768,58 +768,58 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Sigrid Clara (Noor)</t>
+          <t>Bao</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>sirid.krishnan@warriorlife.net</t>
+          <t>bao.pereira@warriorlife.net</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>9/11/2025 22:19:27</t>
+          <t>9/12/2025 10:28:31</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kasper</t>
+          <t>Edda</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kalani</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -830,32 +830,32 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Ainsley</t>
+          <t>Naila</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Pandit</t>
+          <t>Solberg</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ainsley.pandit@warriorlife.net</t>
+          <t>naila.solberg@warriorlife.net</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>9/12/2025 19:09:11</t>
+          <t>9/11/2025 22:02:10</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -866,22 +866,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kasper</t>
+          <t>Remy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kalani</t>
+          <t>Milburn</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -892,32 +892,32 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Theo</t>
+          <t>Isla</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Sathe</t>
+          <t>Baptiste</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>theo.sathe@warriorlife.net</t>
+          <t>isla.baptiste@warriorlife.net</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>9/13/2025 11:02:16</t>
+          <t>9/11/2025 22:36:25</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -928,22 +928,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kasper</t>
+          <t>Remy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kalani</t>
+          <t>Milburn</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -954,32 +954,32 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Klara</t>
+          <t>Ravi</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Serrano</t>
+          <t>Jensen</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>klara.serrano@warriorlife.net</t>
+          <t>ravi.jensen@warriorlife.net</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>9/12/2025 19:50:55</t>
+          <t>9/11/2025 18:54:15</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -990,22 +990,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kasper</t>
+          <t>Remy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kalani</t>
+          <t>Milburn</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -1016,17 +1016,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Quinn</t>
+          <t>Freya</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Souza</t>
+          <t>Kowalczyk</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1036,12 +1036,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>peeira.souza@warriorlife.net</t>
+          <t>freya.kowalczyk@warriorlife.net</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>9/13/2025 11:03:00</t>
+          <t>9/12/2025 17:29:36</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1052,22 +1052,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kasper</t>
+          <t>Remy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kalani</t>
+          <t>Milburn</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1078,17 +1078,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Vance Avani</t>
+          <t>Kalina</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Souza</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>ct.souza@warriorlife.net</t>
+          <t>kalina.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>9/11/2025 22:55:43</t>
+          <t>9/11/2025 22:43:05</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1114,22 +1114,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kasper</t>
+          <t>Remy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kalani</t>
+          <t>Milburn</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -1140,17 +1140,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Andre</t>
+          <t>Gita</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Zeidler</t>
+          <t>Zabala</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>t.zeidler@warriorlife.net</t>
+          <t>gita.zabala@warriorlife.net</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>9/11/2025 22:55:30</t>
+          <t>9/11/2025 23:10:27</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1176,22 +1176,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tadeo</t>
+          <t>Solene</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Loureiro</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -1202,32 +1202,32 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Neel</t>
+          <t>Xanthe</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Falconer</t>
+          <t>Delacroix</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>neel.falconer@warriorlife.net</t>
+          <t>xanthe.delacroix@warriorlife.net</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>9/11/2025 23:10:24</t>
+          <t>9/11/2025 19:54:59</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1238,22 +1238,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tadeo</t>
+          <t>Solene</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Loureiro</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -1264,32 +1264,32 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Gia</t>
+          <t>Hugo</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Ferraro</t>
+          <t>Farooqi</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>gia.ferraro@warriorlife.net</t>
+          <t>hugo.farooqi@warriorlife.net</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>9/12/2025 22:13:40</t>
+          <t>9/12/2025 7:48:58</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tadeo</t>
+          <t>Solene</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Loureiro</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -1326,32 +1326,32 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Ugo</t>
+          <t>Javier</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Lundgren</t>
+          <t>Jarvis</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ugo.lundgren@warriorlife.net</t>
+          <t>javier.jarvis@warriorlife.net</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>9/12/2025 15:54:11</t>
+          <t>9/12/2025 17:26:37</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1362,22 +1362,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tadeo</t>
+          <t>Solene</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Loureiro</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -1388,17 +1388,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Mona</t>
+          <t>Pavel</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Montague</t>
+          <t>Maldonado</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>mona.montague@warriorlife.net</t>
+          <t>pavel.maldonado@warriorlife.net</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>9/11/2025 22:08:40</t>
+          <t>9/12/2025 14:09:36</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1424,22 +1424,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tadeo</t>
+          <t>Solene</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Loureiro</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Yusuf</t>
+          <t>Teodora</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Reyes</t>
+          <t>Marchetti</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1470,12 +1470,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>yusuf.reyes@warriorlife.net</t>
+          <t>zoa.marchetti@warriorlife.net</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>9/11/2025 22:00:40</t>
+          <t>9/12/2025 20:08:31</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1486,22 +1486,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tadeo</t>
+          <t>Solene</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Loureiro</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1512,32 +1512,32 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Magnus</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Shanley</t>
+          <t>Sibanda</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>aurora.rugieroshanley@warriorlife.net</t>
+          <t>magnus.sibanda@warriorlife.net</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>9/12/2025 14:01:19</t>
+          <t>9/12/2025 21:17:27</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1548,22 +1548,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hana</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Milburn</t>
+          <t>Obradovic</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Community Awareness Project (PMCA)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1579,12 +1579,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Beatriz</t>
+          <t>Cyrus</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Dalmau</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>beatriz.krishnan@warriorlife.net</t>
+          <t>cyrus.dalmau@warriorlife.net</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>9/11/2025 11:50:43</t>
+          <t>9/12/2025 12:47:50</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -1610,22 +1610,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hana</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Milburn</t>
+          <t>Obradovic</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Community Awareness Project (PMCA)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Mariam</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Mikkelsen</t>
+          <t>Mahmood</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>gabriel.mikkelsen@warriorlife.net</t>
+          <t>mariam.mahmood@warriorlife.net</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>9/12/2025 22:12:33</t>
+          <t>9/11/2025 22:15:52</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -1672,22 +1672,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hana</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Milburn</t>
+          <t>Obradovic</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Community Awareness Project (PMCA)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Noor</t>
+          <t>Nasir</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Renard</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1718,12 +1718,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>noor.renard@warriorlife.net</t>
+          <t>nasir.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>9/12/2025 22:12:36</t>
+          <t>9/12/2025 6:12:21</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -1734,22 +1734,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hana</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Milburn</t>
+          <t>Obradovic</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Community Awareness Project (PMCA)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1765,12 +1765,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Soren</t>
+          <t>Sinead</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Rosales</t>
+          <t>Odhiambo</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>soren.rosales@warriorlife.net</t>
+          <t>sinead.odhiambo@warriorlife.net</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>9/12/2025 20:14:49</t>
+          <t>9/12/2025 15:12:58</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hana</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Milburn</t>
+          <t>Obradovic</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Community Awareness Project (PMCA)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1827,27 +1827,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Declan</t>
+          <t>Mira</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Sotelo</t>
+          <t>Ravindran</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>declan.sotelo@warriorlife.net</t>
+          <t>mirra.ravindran@warriorlife.net</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>9/13/2025 8:58:25</t>
+          <t>9/9/2025 8:01:17</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -1858,22 +1858,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hana</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Milburn</t>
+          <t>Obradovic</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Community Awareness Project (PMCA)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -1889,12 +1889,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Kavya</t>
+          <t>Vivienne</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Wahlberg</t>
+          <t>Zambrano</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>kavya.wahlberg@warriorlife.net</t>
+          <t>vivienne.zambrano@warriorlife.net</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>9/12/2025 16:26:38</t>
+          <t>9/12/2025 9:55:11</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -1920,22 +1920,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sania</t>
+          <t>Zara</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Morales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -1946,32 +1946,32 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Ravi</t>
+          <t>Angelo</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>Khatri</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>ravi.jensen@warriorlife.net</t>
+          <t>angelo.khatri@warriorlife.net</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>9/11/2025 18:54:15</t>
+          <t>9/11/2025 22:19:08</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -1982,22 +1982,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sania</t>
+          <t>Zara</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Morales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -2013,12 +2013,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Florian</t>
+          <t>Sigrid Clara (Noor)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Rautio</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2028,12 +2028,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>florian.rautio@warriorlife.net</t>
+          <t>sirid.krishnan@warriorlife.net</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>9/12/2025 7:27:01</t>
+          <t>9/11/2025 22:19:27</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -2044,22 +2044,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sania</t>
+          <t>Zara</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Morales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -2075,12 +2075,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Fiona</t>
+          <t>Florian</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Silveira</t>
+          <t>Rautio</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2090,12 +2090,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>fiona.silveira@warriorlife.net</t>
+          <t>florian.rautio@warriorlife.net</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>9/12/2025 7:58:41</t>
+          <t>9/12/2025 7:27:01</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -2106,22 +2106,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sania</t>
+          <t>Zara</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Morales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -2132,32 +2132,32 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Gita</t>
+          <t>Fiona</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Zabala</t>
+          <t>Silveira</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>gita.zabala@warriorlife.net</t>
+          <t>fiona.silveira@warriorlife.net</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>9/11/2025 23:10:27</t>
+          <t>9/12/2025 7:58:41</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -2168,22 +2168,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sania</t>
+          <t>Zara</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Morales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -2230,12 +2230,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Solene</t>
+          <t>Darius</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -2256,32 +2256,32 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Priya</t>
+          <t>Beatriz</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Balakrishnan</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>priya.balakrishnan@warriorlife.net</t>
+          <t>beatriz.krishnan@warriorlife.net</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>9/12/2025 6:40:22</t>
+          <t>9/11/2025 11:50:43</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -2292,12 +2292,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Solene</t>
+          <t>Darius</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -2318,32 +2318,32 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Vidya</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Karimi</t>
+          <t>Mikkelsen</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>vidya.karimi@warriorlife.net</t>
+          <t>gabriel.mikkelsen@warriorlife.net</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>9/11/2025 18:58:33</t>
+          <t>9/12/2025 22:12:33</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -2354,12 +2354,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Solene</t>
+          <t>Darius</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -2380,32 +2380,32 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Milena</t>
+          <t>Noor</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Renard</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>milena.moreau@warriorlife.net</t>
+          <t>noor.renard@warriorlife.net</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>9/11/2025 18:54:26</t>
+          <t>9/12/2025 22:12:36</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -2416,12 +2416,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Solene</t>
+          <t>Darius</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -2442,32 +2442,32 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Bao</t>
+          <t>Soren</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Rosales</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>bao.pereira@warriorlife.net</t>
+          <t>soren.rosales@warriorlife.net</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>9/12/2025 10:28:31</t>
+          <t>9/12/2025 20:14:49</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -2478,12 +2478,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Solene</t>
+          <t>Darius</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -2504,17 +2504,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Gita</t>
+          <t>Declan</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Ponce</t>
+          <t>Sotelo</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>gita.ponce@warriorlife.net</t>
+          <t>declan.sotelo@warriorlife.net</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>9/11/2025 18:57:38</t>
+          <t>9/13/2025 8:58:25</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -2540,12 +2540,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Solene</t>
+          <t>Darius</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -2566,32 +2566,32 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Naila</t>
+          <t>Kavya</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Solberg</t>
+          <t>Wahlberg</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>naila.solberg@warriorlife.net</t>
+          <t>kavya.wahlberg@warriorlife.net</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>9/11/2025 22:02:10</t>
+          <t>9/12/2025 16:26:38</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -2602,12 +2602,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Zola</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Obradovic</t>
+          <t>Shaikh</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Isla</t>
+          <t>Arjun</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Baptiste</t>
+          <t>Duran</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2648,12 +2648,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>isla.baptiste@warriorlife.net</t>
+          <t>arjun.duran@warriorlife.net</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>9/11/2025 22:36:25</t>
+          <t>9/12/2025 14:43:47</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -2664,12 +2664,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Zola</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Obradovic</t>
+          <t>Shaikh</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -2690,17 +2690,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Freya</t>
+          <t>Zola</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Giordano</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2710,12 +2710,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>freya.kowalczyk@warriorlife.net</t>
+          <t>zola.giordano@warriorlife.net</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>9/12/2025 17:29:36</t>
+          <t>9/12/2025 14:43:51</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -2726,12 +2726,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Zola</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Obradovic</t>
+          <t>Shaikh</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -2752,17 +2752,17 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Phoebe</t>
+          <t>Yasmin</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Sandoval</t>
+          <t>Ingersoll</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2772,12 +2772,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>phoebe.sandoval@warriorlife.net</t>
+          <t>yasmin.ingersoll@warriorlife.net</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>9/10/2025 18:24:07</t>
+          <t>9/11/2025 22:14:07</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Zola</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Obradovic</t>
+          <t>Shaikh</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -2814,32 +2814,32 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Kalina</t>
+          <t>Ahana</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Requena</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>kalina.sifuentes@warriorlife.net</t>
+          <t>ahana.vargas@warriorlife.net</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>9/11/2025 22:43:05</t>
+          <t>9/12/2025 9:20:27</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -2850,12 +2850,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Zola</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Obradovic</t>
+          <t>Shaikh</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -2876,32 +2876,32 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Zola</t>
+          <t>ravi</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Ugarte</t>
+          <t>nkemdirim</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>zola.ugarte@warriorlife.net</t>
+          <t>ravi.nkemdirim@warriorlife.net</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>9/10/2025 18:24:13</t>
+          <t>9/11/2025 22:16:21</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -2912,12 +2912,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Darius</t>
+          <t>Diya</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -2938,17 +2938,17 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Xanthe</t>
+          <t>Hadley</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Delacroix</t>
+          <t>Hakim</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>xanthe.delacroix@warriorlife.net</t>
+          <t>hadley.hakim@warriorlife.net</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>9/11/2025 19:54:59</t>
+          <t>9/12/2025 12:21:40</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -2974,12 +2974,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Darius</t>
+          <t>Diya</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -3000,32 +3000,32 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Hugo</t>
+          <t>Tuan</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Farooqi</t>
+          <t>Hartley</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>hugo.farooqi@warriorlife.net</t>
+          <t>tuan.hartley@warriorlife.net</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>9/12/2025 7:48:58</t>
+          <t>9/10/2025 15:40:55</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -3036,12 +3036,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Darius</t>
+          <t>Diya</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -3062,32 +3062,32 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Javier</t>
+          <t>Devika</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Jarvis</t>
+          <t>Olivares</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>javier.jarvis@warriorlife.net</t>
+          <t>devika.olivares@warriorlife.net</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>9/12/2025 17:26:37</t>
+          <t>9/12/2025 17:54:21</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -3098,12 +3098,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Darius</t>
+          <t>Diya</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -3124,32 +3124,32 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Pavel</t>
+          <t>Harlow</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Maldonado</t>
+          <t>Savage</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>pavel.maldonado@warriorlife.net</t>
+          <t>harlow.savage@warriorlife.net</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>9/12/2025 14:09:36</t>
+          <t>9/12/2025 13:10:47</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -3160,12 +3160,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Darius</t>
+          <t>Diya</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -3186,48 +3186,48 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Teodora</t>
+          <t>Shalini</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Marchetti</t>
+          <t>Wickham</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>zoa.marchetti@warriorlife.net</t>
+          <t>shalini.wickham@warriorlife.net</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>9/12/2025 20:08:31</t>
+          <t>9/12/2025 14:13:43</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Darius</t>
+          <t>Kavya</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Sotelo</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Financial Consulting (FCE)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -3248,32 +3248,32 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Magnus</t>
+          <t>Ainsley</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Sibanda</t>
+          <t>Pandit</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>magnus.sibanda@warriorlife.net</t>
+          <t>ainsley.pandit@warriorlife.net</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>9/12/2025 21:17:27</t>
+          <t>9/12/2025 19:09:11</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -3284,22 +3284,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Hina</t>
+          <t>Kavya</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sepulveda</t>
+          <t>Sotelo</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Financial Consulting (FCE)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -3310,32 +3310,32 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Arjun</t>
+          <t>Theo</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Duran</t>
+          <t>Sathe</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>arjun.duran@warriorlife.net</t>
+          <t>theo.sathe@warriorlife.net</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>9/12/2025 14:43:47</t>
+          <t>9/13/2025 11:02:16</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -3346,22 +3346,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Hina</t>
+          <t>Kavya</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sepulveda</t>
+          <t>Sotelo</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Financial Consulting (FCE)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -3372,17 +3372,17 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Zola</t>
+          <t>Klara</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Giordano</t>
+          <t>Serrano</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>zola.giordano@warriorlife.net</t>
+          <t>klara.serrano@warriorlife.net</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>9/12/2025 14:43:51</t>
+          <t>9/12/2025 19:50:55</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -3408,22 +3408,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Hina</t>
+          <t>Kavya</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sepulveda</t>
+          <t>Sotelo</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Financial Consulting (FCE)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -3434,32 +3434,32 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Yasmin</t>
+          <t>Quinn</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Ingersoll</t>
+          <t>Souza</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>yasmin.ingersoll@warriorlife.net</t>
+          <t>peeira.souza@warriorlife.net</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>9/11/2025 22:14:07</t>
+          <t>9/13/2025 11:03:00</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -3470,22 +3470,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Hina</t>
+          <t>Kavya</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sepulveda</t>
+          <t>Sotelo</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Financial Consulting (FCE)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -3496,32 +3496,32 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Ahana</t>
+          <t>Vance Avani</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Requena</t>
+          <t>Souza</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>ahana.vargas@warriorlife.net</t>
+          <t>ct.souza@warriorlife.net</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>9/12/2025 9:20:27</t>
+          <t>9/11/2025 22:55:43</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -3532,22 +3532,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Hina</t>
+          <t>Kavya</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sepulveda</t>
+          <t>Sotelo</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Financial Consulting (FCE)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -3558,17 +3558,17 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>ravi</t>
+          <t>Andre</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>nkemdirim</t>
+          <t>Zeidler</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3578,12 +3578,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>ravi.nkemdirim@warriorlife.net</t>
+          <t>t.zeidler@warriorlife.net</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>9/11/2025 22:16:21</t>
+          <t>9/11/2025 22:55:30</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -3620,17 +3620,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Cyrus</t>
+          <t>Neel</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Dalmau</t>
+          <t>Falconer</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>cyrus.dalmau@warriorlife.net</t>
+          <t>neel.falconer@warriorlife.net</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>9/12/2025 12:47:50</t>
+          <t>9/11/2025 23:10:24</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -3682,32 +3682,32 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Mariam</t>
+          <t>Gia</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Mahmood</t>
+          <t>Ferraro</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>mariam.mahmood@warriorlife.net</t>
+          <t>gia.ferraro@warriorlife.net</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>9/11/2025 22:15:52</t>
+          <t>9/12/2025 22:13:40</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -3744,17 +3744,17 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Nasir</t>
+          <t>Ugo</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Lundgren</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>nasir.moreau@warriorlife.net</t>
+          <t>ugo.lundgren@warriorlife.net</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>9/12/2025 6:12:21</t>
+          <t>9/12/2025 15:54:11</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -3806,17 +3806,17 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Sinead</t>
+          <t>Mona</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Odhiambo</t>
+          <t>Montague</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3826,12 +3826,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>sinead.odhiambo@warriorlife.net</t>
+          <t>mona.montague@warriorlife.net</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>9/12/2025 15:12:58</t>
+          <t>9/11/2025 22:08:40</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -3868,32 +3868,32 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Mira</t>
+          <t>Yusuf</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Ravindran</t>
+          <t>Reyes</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>mirra.ravindran@warriorlife.net</t>
+          <t>yusuf.reyes@warriorlife.net</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>9/9/2025 8:01:17</t>
+          <t>9/11/2025 22:00:40</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -3930,17 +3930,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Vivienne</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Zambrano</t>
+          <t>Shanley</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>vivienne.zambrano@warriorlife.net</t>
+          <t>aurora.rugieroshanley@warriorlife.net</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>9/12/2025 9:55:11</t>
+          <t>9/12/2025 14:01:19</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -3966,22 +3966,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Stellan</t>
+          <t>delphine</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>zabala</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -3992,17 +3992,17 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Hadley</t>
+          <t>Vidya</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Hakim</t>
+          <t>Karimi</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>hadley.hakim@warriorlife.net</t>
+          <t>vidya.karimi@warriorlife.net</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>9/12/2025 12:21:40</t>
+          <t>9/11/2025 18:58:33</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -4028,22 +4028,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Stellan</t>
+          <t>delphine</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>zabala</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -4054,32 +4054,32 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Tuan</t>
+          <t>Milena</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Hartley</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>tuan.hartley@warriorlife.net</t>
+          <t>milena.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>9/10/2025 15:40:55</t>
+          <t>9/11/2025 18:54:26</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -4090,22 +4090,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Stellan</t>
+          <t>delphine</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>zabala</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -4116,17 +4116,17 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Devika</t>
+          <t>Gita</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Olivares</t>
+          <t>Ponce</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>devika.olivares@warriorlife.net</t>
+          <t>gita.ponce@warriorlife.net</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>9/12/2025 17:54:21</t>
+          <t>9/11/2025 18:57:38</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -4152,22 +4152,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Stellan</t>
+          <t>delphine</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>zabala</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -4178,32 +4178,32 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Harlow</t>
+          <t>Phoebe</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Savage</t>
+          <t>Sandoval</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>harlow.savage@warriorlife.net</t>
+          <t>phoebe.sandoval@warriorlife.net</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>9/12/2025 13:10:47</t>
+          <t>9/10/2025 18:24:07</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -4214,22 +4214,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Stellan</t>
+          <t>delphine</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>zabala</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -4240,17 +4240,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Shalini</t>
+          <t>Zola</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Wickham</t>
+          <t>Ugarte</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>shalini.wickham@warriorlife.net</t>
+          <t>zola.ugarte@warriorlife.net</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>9/12/2025 14:13:43</t>
+          <t>9/10/2025 18:24:13</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -4276,12 +4276,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Hedda</t>
+          <t>Lila</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ibarra</t>
+          <t>Granados</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Business Solutions Project (PMBS)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -4302,32 +4302,32 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Athena</t>
+          <t>Indira</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Dumont</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>athena.dumont@warriorlife.net</t>
+          <t>indira.andersen@warriorlife.net</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>9/11/2025 22:34:17</t>
+          <t>9/12/2025 14:52:00</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -4338,12 +4338,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Hedda</t>
+          <t>Lila</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ibarra</t>
+          <t>Granados</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Business Solutions Project (PMBS)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -4364,17 +4364,17 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Naila</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Gagnon</t>
+          <t>Beaumont</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>naila.gagnon@warriorlife.net</t>
+          <t>gabriel.beaumont@warriorlife.net</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>9/10/2025 14:32:40</t>
+          <t>9/11/2025 22:07:49</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -4400,12 +4400,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Hedda</t>
+          <t>Lila</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ibarra</t>
+          <t>Granados</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Business Solutions Project (PMBS)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -4426,17 +4426,17 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Imogen Maeve</t>
+          <t>Nalini</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>Laghari</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>maiam.jensen@warriorlife.net</t>
+          <t>nalini.laghari@warriorlife.net</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>9/11/2025 23:40:36</t>
+          <t>9/11/2025 22:10:45</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -4462,12 +4462,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Hedda</t>
+          <t>Lila</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ibarra</t>
+          <t>Granados</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Business Solutions Project (PMBS)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -4488,32 +4488,32 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Raina</t>
+          <t>Jian</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Melendez</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>raina.melendez@warriorlife.net</t>
+          <t>jian.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>9/12/2025 8:41:42</t>
+          <t>9/11/2025 22:12:23</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -4524,12 +4524,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Hedda</t>
+          <t>Lila</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ibarra</t>
+          <t>Granados</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Business Solutions Project (PMBS)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -4550,58 +4550,58 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Rhys</t>
+          <t>Ramona</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>katayama</t>
+          <t>Nascimento</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>rhys.katayama@warriorlife.net</t>
+          <t>ramona.nascimento@warriorlife.net</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>9/10/2025 20:12:09</t>
+          <t>9/12/2025 7:53:24</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Edda</t>
+          <t>Lila</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Granados</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+          <t>Business Solutions Project (PMBS)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -4617,27 +4617,27 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Indira</t>
+          <t>Nils</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Vasquez</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>indira.andersen@warriorlife.net</t>
+          <t>nils.vasquez@warriorlife.net</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>9/12/2025 14:52:00</t>
+          <t>9/12/2025 7:55:43</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -4648,22 +4648,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Edda</t>
+          <t>Hedda</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Ibarra</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -4674,32 +4674,32 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Eamon</t>
+          <t>Davina</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Kasprzak</t>
+          <t>Avila</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>eamon.kasprzak@warriorlife.net</t>
+          <t>davina.avila@warriorlife.net</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>9/13/2025 6:42:32</t>
+          <t>9/12/2025 7:55:09</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -4710,22 +4710,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Edda</t>
+          <t>Hedda</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Ibarra</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Jian</t>
+          <t>Felicity</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Avila</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>jian.moreau@warriorlife.net</t>
+          <t>felicity.avila@warriorlife.net</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>9/11/2025 22:12:23</t>
+          <t>9/12/2025 8:02:01</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -4772,22 +4772,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Edda</t>
+          <t>Hedda</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Ibarra</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -4803,12 +4803,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Ramona</t>
+          <t>Oscar</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Nascimento</t>
+          <t>Draper</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4818,12 +4818,12 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>ramona.nascimento@warriorlife.net</t>
+          <t>oscar.draper@warriorlife.net</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>9/12/2025 7:53:24</t>
+          <t>9/12/2025 12:35:28</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -4834,22 +4834,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Edda</t>
+          <t>Hedda</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Ibarra</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -4860,32 +4860,32 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Jarrah</t>
+          <t>Anders</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Ruggiero</t>
+          <t>Havili</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>jarrah.ruggiero@warriorlife.net</t>
+          <t>anders.havili@warriorlife.net</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>9/11/2025 22:00:44</t>
+          <t>9/12/2025 13:38:37</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -4896,22 +4896,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Edda</t>
+          <t>Hedda</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Ibarra</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -4927,12 +4927,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Nils</t>
+          <t>Aria</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Vasquez</t>
+          <t>Ilyas</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4942,38 +4942,38 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>nils.vasquez@warriorlife.net</t>
+          <t>aria.ilyas@warriorlife.net</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>9/12/2025 7:55:43</t>
+          <t>9/12/2025 13:40:41</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Naila</t>
+          <t>Hedda</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Ibarra</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
@@ -4984,32 +4984,32 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Aiden-Bodhi</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Bergstrom</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>linrui.bergstrom@warriorlife.net</t>
+          <t>aidenbodhi.vargas@warriorlife.net</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>9/12/2025 14:01:32</t>
+          <t>9/12/2025 12:31:44</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -5020,22 +5020,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Naila</t>
+          <t>Annika</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Jensen</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -5046,32 +5046,32 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Lena</t>
+          <t>Kabir</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Doyle</t>
+          <t>Bakke</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>an.doyle@warriorlife.net</t>
+          <t>s.bakke@warriorlife.net</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>9/11/2025 22:13:25</t>
+          <t>9/13/2025 0:03:52</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -5082,22 +5082,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Naila</t>
+          <t>Annika</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Jensen</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
@@ -5108,32 +5108,32 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Nara</t>
+          <t>Suri</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Garrido</t>
+          <t>Escobar</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>nara.garrido@warriorlife.net</t>
+          <t>suri.escobar@warriorlife.net</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>9/11/2025 22:28:55</t>
+          <t>9/12/2025 23:28:28</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -5144,22 +5144,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Naila</t>
+          <t>Annika</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Jensen</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
@@ -5170,17 +5170,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Theo</t>
+          <t>Esteban</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Herrera</t>
+          <t>Haddad</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>theo.herrera@warriorlife.net</t>
+          <t>esteban.haddad@warriorlife.net</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>9/12/2025 10:59:12</t>
+          <t>9/12/2025 18:44:57</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -5206,22 +5206,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Naila</t>
+          <t>Annika</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Jensen</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -5232,32 +5232,32 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Wren</t>
+          <t>Hassan</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Mikkelsen</t>
+          <t>Hollingsworth</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>wren.mikkelsen@warriorlife.net</t>
+          <t>hassan.hollingsworth@warriorlife.net</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>9/12/2025 7:15:29</t>
+          <t>9/12/2025 21:25:44</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -5268,22 +5268,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Naila</t>
+          <t>Annika</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Jensen</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
@@ -5294,17 +5294,17 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Imani</t>
+          <t>dashiell</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>imogen</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>manus.sifuentes@warriorlife.net</t>
+          <t>dashiell.imogen@warriorlife.net</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>9/11/2025 21:55:46</t>
+          <t>9/11/2025 21:37:29</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -5330,22 +5330,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ulla</t>
+          <t>Tadeo</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Mariotti</t>
+          <t>Mercado</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Community Awareness Project (PMCA)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
@@ -5356,32 +5356,32 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Eitan</t>
+          <t>Kiran</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Lauridsen</t>
+          <t>Chidozie</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>eitan.lauridsen@warriorlife.net</t>
+          <t>kiran.chidozie@warriorlife.net</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>9/12/2025 14:11:35</t>
+          <t>9/11/2025 22:22:21</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -5392,22 +5392,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ulla</t>
+          <t>Tadeo</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Mariotti</t>
+          <t>Mercado</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Community Awareness Project (PMCA)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
@@ -5418,32 +5418,32 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Olamide</t>
+          <t>Eamon</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Noorani</t>
+          <t>Kasprzak</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>olamide.noorani@warriorlife.net</t>
+          <t>eamon.kasprzak@warriorlife.net</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>9/12/2025 14:12:28</t>
+          <t>9/13/2025 6:42:32</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -5454,22 +5454,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ulla</t>
+          <t>Tadeo</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Mariotti</t>
+          <t>Mercado</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Community Awareness Project (PMCA)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
@@ -5480,32 +5480,32 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Manon Nuri</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Nuri</t>
+          <t>Mancini</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>manon.nuri@warriorlife.net</t>
+          <t>camila.mancini@warriorlife.net</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>9/12/2025 14:13:11</t>
+          <t>9/11/2025 22:38:14</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -5516,22 +5516,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ulla</t>
+          <t>Tadeo</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Mariotti</t>
+          <t>Mercado</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Community Awareness Project (PMCA)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
@@ -5542,32 +5542,32 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Zelda</t>
+          <t>Rhys</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Tiwari</t>
+          <t>Mubarak</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>zelda.tiwari@warriorlife.net</t>
+          <t>rhys.mubarak@warriorlife.net</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>9/12/2025 21:53:17</t>
+          <t>9/11/2025 22:10:56</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -5578,22 +5578,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ulla</t>
+          <t>Tadeo</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Mariotti</t>
+          <t>Mercado</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Community Awareness Project (PMCA)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
@@ -5604,32 +5604,32 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Celine</t>
+          <t>Vikram</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Wadsworth</t>
+          <t>Vaidya</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>celine.wadsworth@warriorlife.net</t>
+          <t>vikram.vaidya@warriorlife.net</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>9/12/2025 14:28:55</t>
+          <t>9/11/2025 22:12:43</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Remy</t>
+          <t>Hana</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5650,12 +5650,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Community Awareness Project (PMCA)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -5666,17 +5666,17 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Oscar</t>
+          <t>Fabian</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Draper</t>
+          <t>Eberhardt</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5686,12 +5686,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>oscar.draper@warriorlife.net</t>
+          <t>v.eberhardt@warriorlife.net</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>9/12/2025 12:35:28</t>
+          <t>9/11/2025 22:25:02</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Remy</t>
+          <t>Hana</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Community Awareness Project (PMCA)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
@@ -5728,32 +5728,32 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Rosalind</t>
+          <t>Sienna</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Gauthier</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>sinead.gauthier@warriorlife.net</t>
+          <t>sienna.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>9/12/2025 7:28:39</t>
+          <t>9/12/2025 10:51:31</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Remy</t>
+          <t>Hana</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Community Awareness Project (PMCA)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
@@ -5790,17 +5790,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Anders</t>
+          <t>Fatima</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Havili</t>
+          <t>Redmond</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>anders.havili@warriorlife.net</t>
+          <t>fatima.redmond@warriorlife.net</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>9/12/2025 13:38:37</t>
+          <t>9/11/2025 21:13:52</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Remy</t>
+          <t>Hana</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5836,12 +5836,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Community Awareness Project (PMCA)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
@@ -5852,17 +5852,17 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Aria</t>
+          <t>Colette</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Ilyas</t>
+          <t>Reinholt</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5872,12 +5872,12 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>aria.ilyas@warriorlife.net</t>
+          <t>colette.reinholt@warriorlife.net</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>9/12/2025 13:40:41</t>
+          <t>9/11/2025 21:37:33</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Remy</t>
+          <t>Hana</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Community Awareness Project (PMCA)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
@@ -5914,32 +5914,32 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Aiden-Bodhi</t>
+          <t>Phoebe</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>sifuentes</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>aidenbodhi.vargas@warriorlife.net</t>
+          <t>phebe.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>9/12/2025 12:31:44</t>
+          <t>9/12/2025 10:51:29</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
@@ -5950,12 +5950,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ilana</t>
+          <t>Danilo</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Nuri</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
@@ -5976,32 +5976,32 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Carmen</t>
+          <t>Athena</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Delacroix</t>
+          <t>Dumont</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>carmen.delacroix@warriorlife.net</t>
+          <t>athena.dumont@warriorlife.net</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>9/12/2025 17:05:07</t>
+          <t>9/11/2025 22:34:17</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -6012,12 +6012,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ilana</t>
+          <t>Danilo</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Nuri</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -6027,7 +6027,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
@@ -6038,32 +6038,32 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Suri</t>
+          <t>Naila</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Escobar</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>suri.escobar@warriorlife.net</t>
+          <t>naila.gagnon@warriorlife.net</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>9/12/2025 23:28:28</t>
+          <t>9/10/2025 14:32:40</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
@@ -6074,12 +6074,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ilana</t>
+          <t>Danilo</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Nuri</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
@@ -6100,32 +6100,32 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Hassan</t>
+          <t>Imogen Maeve</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Hollingsworth</t>
+          <t>Jensen</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>hassan.hollingsworth@warriorlife.net</t>
+          <t>maiam.jensen@warriorlife.net</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>9/12/2025 21:25:44</t>
+          <t>9/11/2025 23:40:36</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
@@ -6136,12 +6136,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ilana</t>
+          <t>Danilo</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Nuri</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
@@ -6162,32 +6162,32 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Cassian</t>
+          <t>Raina</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Nuri</t>
+          <t>Melendez</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>cassian.nuri@warriorlife.net</t>
+          <t>raina.melendez@warriorlife.net</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>9/12/2025 14:14:54</t>
+          <t>9/12/2025 8:41:42</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ilana</t>
+          <t>Danilo</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Nuri</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
@@ -6224,32 +6224,32 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Aarav</t>
+          <t>Rhys</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Ostrowski</t>
+          <t>katayama</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>d.brannordstrom@warriorlife.net</t>
+          <t>rhys.katayama@warriorlife.net</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>9/12/2025 14:14:36</t>
+          <t>9/10/2025 20:12:09</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Zara</t>
+          <t>Ilana</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
@@ -6286,32 +6286,32 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Kabir</t>
+          <t>Carmen</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Bakke</t>
+          <t>Delacroix</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>s.bakke@warriorlife.net</t>
+          <t>carmen.delacroix@warriorlife.net</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>9/13/2025 0:03:52</t>
+          <t>9/12/2025 17:05:07</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Zara</t>
+          <t>Ilana</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6332,12 +6332,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
@@ -6348,17 +6348,17 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Rosalind</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Dhillon</t>
+          <t>Gauthier</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6368,12 +6368,12 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>renata.dhillon@warriorlife.net</t>
+          <t>sinead.gauthier@warriorlife.net</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>9/9/2025 9:47:37</t>
+          <t>9/12/2025 7:28:39</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Zara</t>
+          <t>Ilana</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -6410,32 +6410,32 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Esteban</t>
+          <t>Kian</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Haddad</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>esteban.haddad@warriorlife.net</t>
+          <t>kian.guerrero@warriorlife.net</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>9/12/2025 18:44:57</t>
+          <t>9/12/2025 10:58:13</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Zara</t>
+          <t>Ilana</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
@@ -6472,32 +6472,32 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Aneesha</t>
+          <t>Cassian</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Zabala</t>
+          <t>Nuri</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>aneesha.zabala@warriorlife.net</t>
+          <t>cassian.nuri@warriorlife.net</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>9/9/2025 8:54:42</t>
+          <t>9/12/2025 14:14:54</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Zara</t>
+          <t>Ilana</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6518,12 +6518,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
@@ -6534,17 +6534,17 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>dashiell</t>
+          <t>Aarav</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>imogen</t>
+          <t>Ostrowski</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6554,28 +6554,28 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>dashiell.imogen@warriorlife.net</t>
+          <t>d.brannordstrom@warriorlife.net</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>9/11/2025 21:37:29</t>
+          <t>9/12/2025 14:14:36</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ivan</t>
+          <t>Ilana</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
@@ -6601,27 +6601,27 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Corin</t>
+          <t>Senna</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Espinoza</t>
+          <t>Petrov</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>corin.espinoza@warriorlife.net</t>
+          <t>senna.petrov@warriorlife.net</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>9/12/2025 7:41:28</t>
+          <t>9/12/2025 10:47:55</t>
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
@@ -6632,12 +6632,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Ivan</t>
+          <t>Hina</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Sepulveda</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
@@ -6663,12 +6663,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Kian</t>
+          <t>Corin</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Guerrero</t>
+          <t>Espinoza</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6678,12 +6678,12 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>kian.guerrero@warriorlife.net</t>
+          <t>corin.espinoza@warriorlife.net</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>9/12/2025 10:58:13</t>
+          <t>9/12/2025 7:41:28</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
@@ -6694,12 +6694,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Ivan</t>
+          <t>Hina</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Sepulveda</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
@@ -6756,12 +6756,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Ivan</t>
+          <t>Hina</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Sepulveda</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
@@ -6787,27 +6787,27 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Senna</t>
+          <t>Jarrah</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Petrov</t>
+          <t>Ruggiero</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>senna.petrov@warriorlife.net</t>
+          <t>jarrah.ruggiero@warriorlife.net</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>9/12/2025 10:47:55</t>
+          <t>9/11/2025 22:00:44</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -6818,12 +6818,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ivan</t>
+          <t>Hina</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Sepulveda</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
@@ -6880,12 +6880,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Ivan</t>
+          <t>Hina</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Sepulveda</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
@@ -6942,22 +6942,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Kavya</t>
+          <t>Ivan</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sotelo</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
@@ -6968,32 +6968,32 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Davina</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Avila</t>
+          <t>Dhillon</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>davina.avila@warriorlife.net</t>
+          <t>renata.dhillon@warriorlife.net</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>9/12/2025 7:55:09</t>
+          <t>9/9/2025 9:47:37</t>
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
@@ -7004,22 +7004,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Kavya</t>
+          <t>Ivan</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sotelo</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
@@ -7030,17 +7030,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Felicity</t>
+          <t>Eitan</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Avila</t>
+          <t>Lauridsen</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>felicity.avila@warriorlife.net</t>
+          <t>eitan.lauridsen@warriorlife.net</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>9/12/2025 8:02:01</t>
+          <t>9/12/2025 14:11:35</t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
@@ -7066,22 +7066,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Kavya</t>
+          <t>Ivan</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Sotelo</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
@@ -7092,32 +7092,32 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Kiran</t>
+          <t>Olamide</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Chidozie</t>
+          <t>Noorani</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>kiran.chidozie@warriorlife.net</t>
+          <t>olamide.noorani@warriorlife.net</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>9/11/2025 22:22:21</t>
+          <t>9/12/2025 14:12:28</t>
         </is>
       </c>
       <c r="N108" t="inlineStr"/>
@@ -7128,22 +7128,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Kavya</t>
+          <t>Ivan</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Sotelo</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
@@ -7154,32 +7154,32 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Manon Nuri</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Mancini</t>
+          <t>Nuri</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>camila.mancini@warriorlife.net</t>
+          <t>manon.nuri@warriorlife.net</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>9/11/2025 22:38:14</t>
+          <t>9/12/2025 14:13:11</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
@@ -7190,22 +7190,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Kavya</t>
+          <t>Ivan</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Sotelo</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
@@ -7216,58 +7216,58 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Rhys</t>
+          <t>Zelda</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Mubarak</t>
+          <t>Tiwari</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>rhys.mubarak@warriorlife.net</t>
+          <t>zelda.tiwari@warriorlife.net</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>9/11/2025 22:10:56</t>
+          <t>9/12/2025 21:53:17</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Kavya</t>
+          <t>Nova</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Sotelo</t>
+          <t>Stanek</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
@@ -7278,32 +7278,32 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Vikram</t>
+          <t>Uma</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Vaidya</t>
+          <t>Madrigal</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>vikram.vaidya@warriorlife.net</t>
+          <t>uma.madrigal@warriorlife.net</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>9/11/2025 22:12:43</t>
+          <t>9/12/2025 16:09:17</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -7345,27 +7345,27 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Uma</t>
+          <t>Idris</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Madrigal</t>
+          <t>Mubarak</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>uma.madrigal@warriorlife.net</t>
+          <t>idris.mubarak@warriorlife.net</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>9/12/2025 16:09:17</t>
+          <t>9/11/2025 22:50:30</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -7407,27 +7407,27 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Idris</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Mubarak</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>idris.mubarak@warriorlife.net</t>
+          <t>ceilialorcan.vargas@warriorlife.net</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>9/11/2025 22:50:30</t>
+          <t>9/12/2025 12:24:12</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -7469,27 +7469,27 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>Nadia</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>Whitlock</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>ceilialorcan.vargas@warriorlife.net</t>
+          <t>nadia.whitlock@warriorlife.net</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>9/12/2025 12:24:12</t>
+          <t>9/12/2025 8:11:14</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -7531,27 +7531,27 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Nadia</t>
+          <t>mateo</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Whitlock</t>
+          <t>sifuentes</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>nadia.whitlock@warriorlife.net</t>
+          <t>weilun.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>9/12/2025 8:11:14</t>
+          <t>9/12/2025 12:27:46</t>
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
@@ -7593,43 +7593,43 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>mateo</t>
+          <t>Kamal</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>sifuentes</t>
+          <t>sorensen</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>weilun.sifuentes@warriorlife.net</t>
+          <t>kamal.sorensen@warriorlife.net</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>9/12/2025 12:27:46</t>
+          <t>9/12/2025 18:30:57</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Nova</t>
+          <t>Stellan</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Stanek</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7655,27 +7655,27 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Kamal</t>
+          <t>Valentina</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>sorensen</t>
+          <t>Achebe</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>kamal.sorensen@warriorlife.net</t>
+          <t>valentina.achebe@warriorlife.net</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>9/12/2025 18:30:57</t>
+          <t>9/11/2025 19:46:16</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -7686,22 +7686,22 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Paloma</t>
+          <t>Stellan</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Zabala</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
@@ -7712,17 +7712,17 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Zelda</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Beaumont</t>
+          <t>Demir</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>gabriel.beaumont@warriorlife.net</t>
+          <t>zelda.demir@warriorlife.net</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>9/11/2025 22:07:49</t>
+          <t>9/12/2025 12:30:51</t>
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
@@ -7748,22 +7748,22 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Paloma</t>
+          <t>Stellan</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Zabala</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
@@ -7774,32 +7774,32 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Yael</t>
+          <t>Tomas</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Caldeira</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>yael.caldeira@warriorlife.net</t>
+          <t>tomas.gagnon@warriorlife.net</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>9/11/2025 22:37:04</t>
+          <t>9/11/2025 21:57:36</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -7810,22 +7810,22 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Paloma</t>
+          <t>Stellan</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Zabala</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
@@ -7836,17 +7836,17 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Alana</t>
+          <t>Vera</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Cisneros</t>
+          <t>Kanellis</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>lelerc.cisneros@warriorlife.net</t>
+          <t>vera.kanellis@warriorlife.net</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>9/12/2025 21:19:28</t>
+          <t>9/12/2025 10:47:36</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -7872,22 +7872,22 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Paloma</t>
+          <t>Stellan</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Zabala</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
@@ -7898,32 +7898,32 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Nalini</t>
+          <t>Lachlan</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Laghari</t>
+          <t>Novak</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>nalini.laghari@warriorlife.net</t>
+          <t>lachlan.novak@warriorlife.net</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>9/11/2025 22:10:45</t>
+          <t>9/11/2025 20:29:20</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -7934,22 +7934,22 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Paloma</t>
+          <t>Stellan</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Zabala</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
@@ -7960,17 +7960,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Sohan</t>
+          <t>Ivo</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Maldonado</t>
+          <t>Wanjiru</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -7980,12 +7980,12 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>kwanming.maldonado@warriorlife.net</t>
+          <t>ivo.wanjiru@warriorlife.net</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>9/11/2025 22:40:20</t>
+          <t>9/12/2025 12:30:38</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
@@ -7996,12 +7996,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>astrid</t>
+          <t>sadie</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>kaufman</t>
+          <t>dahlberg</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Community Giving Project (PMCG)</t>
         </is>
       </c>
       <c r="F123" t="inlineStr"/>
@@ -8022,17 +8022,17 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Valentina</t>
+          <t>Samara</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Achebe</t>
+          <t>Bergstrom</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>valentina.achebe@warriorlife.net</t>
+          <t>linrui.bergstrom@warriorlife.net</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>9/11/2025 19:46:16</t>
+          <t>9/12/2025 14:01:32</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
@@ -8058,12 +8058,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>astrid</t>
+          <t>sadie</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>kaufman</t>
+          <t>dahlberg</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Community Giving Project (PMCG)</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
@@ -8084,32 +8084,32 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Zelda</t>
+          <t>Lena</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Demir</t>
+          <t>Doyle</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>zelda.demir@warriorlife.net</t>
+          <t>an.doyle@warriorlife.net</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>9/12/2025 12:30:51</t>
+          <t>9/11/2025 22:13:25</t>
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
@@ -8120,12 +8120,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>astrid</t>
+          <t>sadie</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>kaufman</t>
+          <t>dahlberg</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Community Giving Project (PMCG)</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
@@ -8146,32 +8146,32 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Tomas</t>
+          <t>Nara</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Gagnon</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>tomas.gagnon@warriorlife.net</t>
+          <t>nara.garrido@warriorlife.net</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>9/11/2025 21:57:36</t>
+          <t>9/11/2025 22:28:55</t>
         </is>
       </c>
       <c r="N125" t="inlineStr"/>
@@ -8182,12 +8182,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>astrid</t>
+          <t>sadie</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>kaufman</t>
+          <t>dahlberg</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Community Giving Project (PMCG)</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
@@ -8208,17 +8208,17 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Vera</t>
+          <t>Theo</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Kanellis</t>
+          <t>Herrera</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>vera.kanellis@warriorlife.net</t>
+          <t>theo.herrera@warriorlife.net</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>9/12/2025 10:47:36</t>
+          <t>9/12/2025 10:59:12</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
@@ -8244,12 +8244,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>astrid</t>
+          <t>sadie</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>kaufman</t>
+          <t>dahlberg</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Community Giving Project (PMCG)</t>
         </is>
       </c>
       <c r="F127" t="inlineStr"/>
@@ -8270,32 +8270,32 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Lachlan</t>
+          <t>Wren</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Novak</t>
+          <t>Mikkelsen</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>lachlan.novak@warriorlife.net</t>
+          <t>wren.mikkelsen@warriorlife.net</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>9/11/2025 20:29:20</t>
+          <t>9/12/2025 7:15:29</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
@@ -8306,12 +8306,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>astrid</t>
+          <t>sadie</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>kaufman</t>
+          <t>dahlberg</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -8321,7 +8321,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Community Giving Project (PMCG)</t>
         </is>
       </c>
       <c r="F128" t="inlineStr"/>
@@ -8332,17 +8332,17 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Ivo</t>
+          <t>Imani</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Wanjiru</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>ivo.wanjiru@warriorlife.net</t>
+          <t>manus.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>9/12/2025 12:30:38</t>
+          <t>9/11/2025 21:55:46</t>
         </is>
       </c>
       <c r="N128" t="inlineStr"/>
@@ -8368,22 +8368,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>delphine</t>
+          <t>astrid</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>zabala</t>
+          <t>kaufman</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
@@ -8399,12 +8399,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Fabian</t>
+          <t>Yael</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Eberhardt</t>
+          <t>Caldeira</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>v.eberhardt@warriorlife.net</t>
+          <t>yael.caldeira@warriorlife.net</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>9/11/2025 22:25:02</t>
+          <t>9/11/2025 22:37:04</t>
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
@@ -8430,22 +8430,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>delphine</t>
+          <t>astrid</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>zabala</t>
+          <t>kaufman</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
@@ -8461,27 +8461,27 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Sienna</t>
+          <t>Alana</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Cisneros</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>sienna.moreau@warriorlife.net</t>
+          <t>lelerc.cisneros@warriorlife.net</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>9/12/2025 10:51:31</t>
+          <t>9/12/2025 21:19:28</t>
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
@@ -8492,22 +8492,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>delphine</t>
+          <t>astrid</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>zabala</t>
+          <t>kaufman</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
@@ -8523,12 +8523,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Fatima</t>
+          <t>Sohan</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Redmond</t>
+          <t>Maldonado</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>fatima.redmond@warriorlife.net</t>
+          <t>kwanming.maldonado@warriorlife.net</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>9/11/2025 21:13:52</t>
+          <t>9/11/2025 22:40:20</t>
         </is>
       </c>
       <c r="N131" t="inlineStr"/>
@@ -8554,22 +8554,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>delphine</t>
+          <t>astrid</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>zabala</t>
+          <t>kaufman</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
@@ -8580,17 +8580,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Colette</t>
+          <t>Celine</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Reinholt</t>
+          <t>Wadsworth</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -8600,12 +8600,12 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>colette.reinholt@warriorlife.net</t>
+          <t>celine.wadsworth@warriorlife.net</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>9/11/2025 21:37:33</t>
+          <t>9/12/2025 14:28:55</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -8616,22 +8616,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>delphine</t>
+          <t>astrid</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>zabala</t>
+          <t>kaufman</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="F133" t="inlineStr"/>
@@ -8642,17 +8642,17 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Phoebe</t>
+          <t>Aneesha</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>sifuentes</t>
+          <t>Zabala</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8662,12 +8662,12 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>phebe.sifuentes@warriorlife.net</t>
+          <t>aneesha.zabala@warriorlife.net</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>9/12/2025 10:51:29</t>
+          <t>9/9/2025 8:54:42</t>
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
@@ -8678,17 +8678,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Danilo</t>
+          <t>Kasper</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Nuri</t>
+          <t>Kalani</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8704,32 +8704,32 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Tarek</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Adeyemi</t>
+          <t>Achebe</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>tarek.adeyemi@warriorlife.net</t>
+          <t>gemma.achebe@warriorlife.net</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>9/12/2025 15:14:00</t>
+          <t>9/12/2025 15:56:03</t>
         </is>
       </c>
       <c r="N134" t="inlineStr"/>
@@ -8740,17 +8740,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Danilo</t>
+          <t>Kasper</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Nuri</t>
+          <t>Kalani</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Malia</t>
+          <t>Chandra</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Fonseca</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>malia.andersen@warriorlife.net</t>
+          <t>chandra.fonseca@warriorlife.net</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>9/12/2025 15:02:39</t>
+          <t>9/11/2025 22:14:39</t>
         </is>
       </c>
       <c r="N135" t="inlineStr"/>
@@ -8802,17 +8802,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Danilo</t>
+          <t>Kasper</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Nuri</t>
+          <t>Kalani</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8828,32 +8828,32 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Svea</t>
+          <t>Anton</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Brandt</t>
+          <t>Mbeki</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>svea.brandt@warriorlife.net</t>
+          <t>anton.mbeki@warriorlife.net</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>9/12/2025 23:13:38</t>
+          <t>9/10/2025 14:35:18</t>
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
@@ -8864,17 +8864,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Danilo</t>
+          <t>Kasper</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Nuri</t>
+          <t>Kalani</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8890,32 +8890,32 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Chiara</t>
+          <t>Saanvi</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Callahan</t>
+          <t>Nazari</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>chiara.callahan@warriorlife.net</t>
+          <t>saanvi.nazari@warriorlife.net</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>9/12/2025 7:45:09</t>
+          <t>9/12/2025 18:50:14</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
@@ -8926,17 +8926,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Danilo</t>
+          <t>Kasper</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Nuri</t>
+          <t>Kalani</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8952,17 +8952,17 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Elara</t>
+          <t>Elias</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Mehrotra</t>
+          <t>Riordan</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>elara.mehrotra@warriorlife.net</t>
+          <t>elias.riordan@warriorlife.net</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>9/12/2025 22:08:36</t>
+          <t>9/12/2025 16:03:03</t>
         </is>
       </c>
       <c r="N138" t="inlineStr"/>
@@ -8988,17 +8988,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Danilo</t>
+          <t>Kasper</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Nuri</t>
+          <t>Kalani</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -9014,32 +9014,32 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Ayaan</t>
+          <t>Tavish</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Villanueva</t>
+          <t>Rivas</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>ayaan.villanueva@warriorlife.net</t>
+          <t>tavish.rivas@warriorlife.net</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>9/12/2025 15:04:57</t>
+          <t>9/12/2025 19:47:03</t>
         </is>
       </c>
       <c r="N139" t="inlineStr"/>
@@ -9050,22 +9050,22 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Zola</t>
+          <t>Naila</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Shaikh</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
+          <t>Financial Consulting (FCE)</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
@@ -9081,12 +9081,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Diya</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Achebe</t>
+          <t>Fitzgerald</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>gemma.achebe@warriorlife.net</t>
+          <t>diya.fitzgerald@warriorlife.net</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>9/12/2025 15:56:03</t>
+          <t>9/13/2025 14:58:43</t>
         </is>
       </c>
       <c r="N140" t="inlineStr"/>
@@ -9112,22 +9112,22 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Zola</t>
+          <t>Naila</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Shaikh</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
+          <t>Financial Consulting (FCE)</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
@@ -9143,27 +9143,27 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Anton</t>
+          <t>Marco</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Mbeki</t>
+          <t>Greenway</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>anton.mbeki@warriorlife.net</t>
+          <t>marco.greenway@warriorlife.net</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>9/10/2025 14:35:18</t>
+          <t>9/12/2025 16:43:28</t>
         </is>
       </c>
       <c r="N141" t="inlineStr"/>
@@ -9174,22 +9174,22 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Zola</t>
+          <t>Naila</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Shaikh</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
+          <t>Financial Consulting (FCE)</t>
         </is>
       </c>
       <c r="F142" t="inlineStr"/>
@@ -9205,27 +9205,27 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Saanvi</t>
+          <t>Emeka</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Nazari</t>
+          <t>Nascimento</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>saanvi.nazari@warriorlife.net</t>
+          <t>emeka.nascimento@warriorlife.net</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>9/12/2025 18:50:14</t>
+          <t>9/12/2025 17:12:18</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
@@ -9236,22 +9236,22 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Zola</t>
+          <t>Naila</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Shaikh</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
+          <t>Financial Consulting (FCE)</t>
         </is>
       </c>
       <c r="F143" t="inlineStr"/>
@@ -9267,12 +9267,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Elias</t>
+          <t>Eero</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Riordan</t>
+          <t>Rothman</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -9282,12 +9282,12 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>elias.riordan@warriorlife.net</t>
+          <t>eero.rothman@warriorlife.net</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>9/12/2025 16:03:03</t>
+          <t>9/12/2025 17:30:29</t>
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
@@ -9298,22 +9298,22 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Zola</t>
+          <t>Naila</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Shaikh</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
+          <t>Financial Consulting (FCE)</t>
         </is>
       </c>
       <c r="F144" t="inlineStr"/>
@@ -9329,27 +9329,27 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Tavish</t>
+          <t>Yael</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Rivas</t>
+          <t>Ruggiero</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>tavish.rivas@warriorlife.net</t>
+          <t>yael.ruggiero@warriorlife.net</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>9/12/2025 19:47:03</t>
+          <t>9/13/2025 11:29:14</t>
         </is>
       </c>
       <c r="N144" t="inlineStr"/>
@@ -9360,22 +9360,22 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Zola</t>
+          <t>Naila</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Shaikh</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
+          <t>Financial Consulting (FCE)</t>
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
@@ -9422,22 +9422,22 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Diya</t>
+          <t>Tadeo</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Loureiro</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Community Giving Project (PMCG)</t>
         </is>
       </c>
       <c r="F146" t="inlineStr"/>
@@ -9448,32 +9448,32 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Event (IMCE)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Shai</t>
+          <t>Tarek</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Darrow</t>
+          <t>Adeyemi</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>shai.darrow@warriorlife.net</t>
+          <t>tarek.adeyemi@warriorlife.net</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>9/12/2025 0:58:27</t>
+          <t>9/12/2025 15:14:00</t>
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
@@ -9484,22 +9484,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Diya</t>
+          <t>Tadeo</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Loureiro</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Community Giving Project (PMCG)</t>
         </is>
       </c>
       <c r="F147" t="inlineStr"/>
@@ -9510,17 +9510,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Diya</t>
+          <t>Malia</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Fitzgerald</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -9530,12 +9530,12 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>diya.fitzgerald@warriorlife.net</t>
+          <t>malia.andersen@warriorlife.net</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>9/13/2025 14:58:43</t>
+          <t>9/12/2025 15:02:39</t>
         </is>
       </c>
       <c r="N147" t="inlineStr"/>
@@ -9546,22 +9546,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Diya</t>
+          <t>Tadeo</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Loureiro</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Community Giving Project (PMCG)</t>
         </is>
       </c>
       <c r="F148" t="inlineStr"/>
@@ -9572,32 +9572,32 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Marco</t>
+          <t>Svea</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Greenway</t>
+          <t>Brandt</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>marco.greenway@warriorlife.net</t>
+          <t>svea.brandt@warriorlife.net</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>9/12/2025 16:43:28</t>
+          <t>9/12/2025 23:13:38</t>
         </is>
       </c>
       <c r="N148" t="inlineStr"/>
@@ -9608,22 +9608,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Diya</t>
+          <t>Tadeo</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Loureiro</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Community Giving Project (PMCG)</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
@@ -9634,17 +9634,17 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Emeka</t>
+          <t>Chiara</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Nascimento</t>
+          <t>Callahan</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>emeka.nascimento@warriorlife.net</t>
+          <t>chiara.callahan@warriorlife.net</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>9/12/2025 17:12:18</t>
+          <t>9/12/2025 7:45:09</t>
         </is>
       </c>
       <c r="N149" t="inlineStr"/>
@@ -9670,22 +9670,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Diya</t>
+          <t>Tadeo</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Loureiro</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Community Giving Project (PMCG)</t>
         </is>
       </c>
       <c r="F150" t="inlineStr"/>
@@ -9696,17 +9696,17 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Eero</t>
+          <t>Elara</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Rothman</t>
+          <t>Mehrotra</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -9716,12 +9716,12 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>eero.rothman@warriorlife.net</t>
+          <t>elara.mehrotra@warriorlife.net</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>9/12/2025 17:30:29</t>
+          <t>9/12/2025 22:08:36</t>
         </is>
       </c>
       <c r="N150" t="inlineStr"/>
@@ -9732,22 +9732,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Diya</t>
+          <t>Tadeo</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Loureiro</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Community Giving Project (PMCG)</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
@@ -9758,32 +9758,32 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Yael</t>
+          <t>Ayaan</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Ruggiero</t>
+          <t>Villanueva</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>yael.ruggiero@warriorlife.net</t>
+          <t>ayaan.villanueva@warriorlife.net</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>9/13/2025 11:29:14</t>
+          <t>9/12/2025 15:04:57</t>
         </is>
       </c>
       <c r="N151" t="inlineStr"/>
@@ -9794,22 +9794,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>sadie</t>
+          <t>Ulla</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>dahlberg</t>
+          <t>Mariotti</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
@@ -9856,22 +9856,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>sadie</t>
+          <t>Ulla</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>dahlberg</t>
+          <t>Mariotti</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
@@ -9882,32 +9882,32 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Integrated Marketing Campaign - Event (IMCE)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Chandra</t>
+          <t>Shai</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Fonseca</t>
+          <t>Darrow</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>chandra.fonseca@warriorlife.net</t>
+          <t>shai.darrow@warriorlife.net</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>9/11/2025 22:14:39</t>
+          <t>9/12/2025 0:58:27</t>
         </is>
       </c>
       <c r="N153" t="inlineStr"/>
@@ -9918,22 +9918,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>sadie</t>
+          <t>Ulla</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>dahlberg</t>
+          <t>Mariotti</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
@@ -9980,22 +9980,22 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>sadie</t>
+          <t>Ulla</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>dahlberg</t>
+          <t>Mariotti</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
@@ -10042,22 +10042,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>sadie</t>
+          <t>Ulla</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>dahlberg</t>
+          <t>Mariotti</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
@@ -10104,22 +10104,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>sadie</t>
+          <t>Ulla</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>dahlberg</t>
+          <t>Mariotti</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -10166,17 +10166,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Annika</t>
+          <t>Sania</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>Morales</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -10228,17 +10228,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Annika</t>
+          <t>Sania</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>Morales</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -10290,17 +10290,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Annika</t>
+          <t>Sania</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>Morales</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -10352,17 +10352,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Annika</t>
+          <t>Sania</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>Morales</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -10414,17 +10414,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Annika</t>
+          <t>Sania</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>Morales</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -10476,17 +10476,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Annika</t>
+          <t>Sania</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>Morales</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10538,17 +10538,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Annika</t>
+          <t>Sania</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>Morales</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10600,22 +10600,22 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Tadeo</t>
+          <t>Paloma</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Mercado</t>
+          <t>Zabala</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Community Awareness Project (PMCA)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="F165" t="inlineStr"/>
@@ -10662,22 +10662,22 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Tadeo</t>
+          <t>Paloma</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Mercado</t>
+          <t>Zabala</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Community Awareness Project (PMCA)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="F166" t="inlineStr"/>
@@ -10724,22 +10724,22 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Tadeo</t>
+          <t>Paloma</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Mercado</t>
+          <t>Zabala</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Community Awareness Project (PMCA)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="F167" t="inlineStr"/>
@@ -10786,22 +10786,22 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Tadeo</t>
+          <t>Paloma</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Mercado</t>
+          <t>Zabala</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Community Awareness Project (PMCA)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="F168" t="inlineStr"/>
@@ -10848,22 +10848,22 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Tadeo</t>
+          <t>Paloma</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Mercado</t>
+          <t>Zabala</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Community Awareness Project (PMCA)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
@@ -10910,22 +10910,22 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Tadeo</t>
+          <t>Paloma</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Mercado</t>
+          <t>Zabala</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Community Awareness Project (PMCA)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="F170" t="inlineStr"/>
@@ -10972,22 +10972,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Tadeo</t>
+          <t>Paloma</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Mercado</t>
+          <t>Zabala</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Community Awareness Project (PMCA)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="F171" t="inlineStr"/>

--- a/MentorPodSorting.xlsx
+++ b/MentorPodSorting.xlsx
@@ -520,32 +520,32 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Priya</t>
+          <t>Lian</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Balakrishnan</t>
+          <t>Callahan</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>priya.balakrishnan@warriorlife.net</t>
+          <t>lian.callahan@warriorlife.net</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>9/12/2025 6:40:22</t>
+          <t>9/10/2025 15:11:54</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -582,17 +582,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Hugo</t>
+          <t>Jian</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Farooqi</t>
+          <t>Jensen</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -602,12 +602,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hugo.farooqi@warriorlife.net</t>
+          <t>jian.jensen@warriorlife.net</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>9/12/2025 7:48:58</t>
+          <t>9/10/2025 15:11:02</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -644,17 +644,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Pavel</t>
+          <t>Angelo</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Maldonado</t>
+          <t>Khatri</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -664,12 +664,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>pavel.maldonado@warriorlife.net</t>
+          <t>angelo.khatri@warriorlife.net</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>9/12/2025 14:09:36</t>
+          <t>9/11/2025 22:19:08</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -706,32 +706,32 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Bao</t>
+          <t>Sigrid Clara (Noor)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>bao.pereira@warriorlife.net</t>
+          <t>sirid.krishnan@warriorlife.net</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>9/12/2025 10:28:31</t>
+          <t>9/11/2025 22:19:27</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -768,32 +768,32 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Phoebe</t>
+          <t>Florian</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Sandoval</t>
+          <t>Rautio</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>phoebe.sandoval@warriorlife.net</t>
+          <t>florian.rautio@warriorlife.net</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>9/10/2025 18:24:07</t>
+          <t>9/12/2025 7:27:01</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -830,32 +830,32 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Naila</t>
+          <t>Fiona</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Solberg</t>
+          <t>Silveira</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>naila.solberg@warriorlife.net</t>
+          <t>fiona.silveira@warriorlife.net</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>9/11/2025 22:02:10</t>
+          <t>9/12/2025 7:58:41</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -892,32 +892,32 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Zola</t>
+          <t>Ingrid</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Ugarte</t>
+          <t>Zavala</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>zola.ugarte@warriorlife.net</t>
+          <t>ingrid.zavala@warriorlife.net</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>9/10/2025 18:24:13</t>
+          <t>9/12/2025 15:16:47</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -954,17 +954,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Zola</t>
+          <t>Gia</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Aguilar</t>
+          <t>Ferraro</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>zola.aguilar@warriorlife.net</t>
+          <t>gia.ferraro@warriorlife.net</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>9/11/2025 22:28:39</t>
+          <t>9/12/2025 22:13:40</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1016,17 +1016,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Xanthe</t>
+          <t>Marco</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Delacroix</t>
+          <t>Greenway</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1036,12 +1036,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>xanthe.delacroix@warriorlife.net</t>
+          <t>marco.greenway@warriorlife.net</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>9/11/2025 19:54:59</t>
+          <t>9/12/2025 16:43:28</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1078,32 +1078,32 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Javier</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Jarvis</t>
+          <t>Mikkelsen</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>javier.jarvis@warriorlife.net</t>
+          <t>gabriel.mikkelsen@warriorlife.net</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>9/12/2025 17:26:37</t>
+          <t>9/12/2025 22:12:33</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1140,17 +1140,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Freya</t>
+          <t>Mona</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Montague</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>freya.kowalczyk@warriorlife.net</t>
+          <t>mona.montague@warriorlife.net</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>9/12/2025 17:29:36</t>
+          <t>9/11/2025 22:08:40</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1202,32 +1202,32 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Teodora</t>
+          <t>Ainsley</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Marchetti</t>
+          <t>Pandit</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>zoa.marchetti@warriorlife.net</t>
+          <t>ainsley.pandit@warriorlife.net</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>9/12/2025 20:08:31</t>
+          <t>9/12/2025 19:09:11</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1264,43 +1264,43 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Magnus</t>
+          <t>Noor</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Sibanda</t>
+          <t>Renard</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>magnus.sibanda@warriorlife.net</t>
+          <t>noor.renard@warriorlife.net</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>9/12/2025 21:17:27</t>
+          <t>9/12/2025 22:12:36</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Remy</t>
+          <t>Hana</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Community Awareness Project (PMCA)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -1326,17 +1326,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Cyrus</t>
+          <t>Klara</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Dalmau</t>
+          <t>Serrano</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>cyrus.dalmau@warriorlife.net</t>
+          <t>klara.serrano@warriorlife.net</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>9/12/2025 12:47:50</t>
+          <t>9/12/2025 19:50:55</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1388,32 +1388,32 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Mariam</t>
+          <t>Priya</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Mahmood</t>
+          <t>Balakrishnan</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>mariam.mahmood@warriorlife.net</t>
+          <t>priya.balakrishnan@warriorlife.net</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>9/11/2025 22:15:52</t>
+          <t>9/12/2025 6:40:22</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Nasir</t>
+          <t>Hugo</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Farooqi</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1470,12 +1470,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>nasir.moreau@warriorlife.net</t>
+          <t>hugo.farooqi@warriorlife.net</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>9/12/2025 6:12:21</t>
+          <t>9/12/2025 7:48:58</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1512,17 +1512,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Sinead</t>
+          <t>Pavel</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Odhiambo</t>
+          <t>Maldonado</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>sinead.odhiambo@warriorlife.net</t>
+          <t>pavel.maldonado@warriorlife.net</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>9/12/2025 15:12:58</t>
+          <t>9/12/2025 14:09:36</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1574,32 +1574,32 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Mira</t>
+          <t>Bao</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Ravindran</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>mirra.ravindran@warriorlife.net</t>
+          <t>bao.pereira@warriorlife.net</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>9/9/2025 8:01:17</t>
+          <t>9/12/2025 10:28:31</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -1636,58 +1636,58 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Vivienne</t>
+          <t>Phoebe</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Zambrano</t>
+          <t>Sandoval</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>vivienne.zambrano@warriorlife.net</t>
+          <t>phoebe.sandoval@warriorlife.net</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>9/12/2025 9:55:11</t>
+          <t>9/10/2025 18:24:07</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Danilo</t>
+          <t>Remy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nuri</t>
+          <t>Milburn</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1703,53 +1703,53 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Isla</t>
+          <t>Naila</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Baptiste</t>
+          <t>Solberg</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>isla.baptiste@warriorlife.net</t>
+          <t>naila.solberg@warriorlife.net</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>9/11/2025 22:36:25</t>
+          <t>9/11/2025 22:02:10</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Danilo</t>
+          <t>Remy</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nuri</t>
+          <t>Milburn</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1765,34 +1765,30 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Ravi</t>
+          <t>Zola</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>Ugarte</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>ravi.jensen@warriorlife.net</t>
+          <t>zola.ugarte@warriorlife.net</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>9/11/2025 18:54:15</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>9/10/2025 18:24:13</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1831,27 +1827,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Vidya</t>
+          <t>Isla</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Karimi</t>
+          <t>Baptiste</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>vidya.karimi@warriorlife.net</t>
+          <t>isla.baptiste@warriorlife.net</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>9/11/2025 18:58:33</t>
+          <t>9/11/2025 22:36:25</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -1893,12 +1889,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Milena</t>
+          <t>Ravi</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Jensen</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1908,15 +1904,19 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>milena.moreau@warriorlife.net</t>
+          <t>ravi.jensen@warriorlife.net</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>9/11/2025 18:54:26</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>9/11/2025 18:54:15</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Gita</t>
+          <t>Vidya</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Ponce</t>
+          <t>Karimi</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1970,12 +1970,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>gita.ponce@warriorlife.net</t>
+          <t>vidya.karimi@warriorlife.net</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>9/11/2025 18:57:38</t>
+          <t>9/11/2025 18:58:33</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -2017,27 +2017,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Kalina</t>
+          <t>Milena</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>kalina.sifuentes@warriorlife.net</t>
+          <t>milena.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>9/11/2025 22:43:05</t>
+          <t>9/11/2025 18:54:26</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -2084,52 +2084,48 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Zabala</t>
+          <t>Ponce</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>gita.zabala@warriorlife.net</t>
+          <t>gita.ponce@warriorlife.net</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>9/11/2025 23:10:27</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>9/11/2025 18:57:38</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Zara</t>
+          <t>Danilo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Nuri</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -2140,17 +2136,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Lian</t>
+          <t>Kalina</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Callahan</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2160,38 +2156,38 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>lian.callahan@warriorlife.net</t>
+          <t>kalina.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>9/10/2025 15:11:54</t>
+          <t>9/11/2025 22:43:05</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Zara</t>
+          <t>Danilo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Nuri</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -2202,35 +2198,39 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Jian</t>
+          <t>Gita</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>Zabala</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>jian.jensen@warriorlife.net</t>
+          <t>gita.zabala@warriorlife.net</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>9/10/2025 15:11:02</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>9/11/2025 23:10:27</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2264,32 +2264,32 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Angelo</t>
+          <t>Zola</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Khatri</t>
+          <t>Aguilar</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>angelo.khatri@warriorlife.net</t>
+          <t>zola.aguilar@warriorlife.net</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>9/11/2025 22:19:08</t>
+          <t>9/11/2025 22:28:39</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -2326,32 +2326,32 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Sigrid Clara (Noor)</t>
+          <t>Xanthe</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Delacroix</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>sirid.krishnan@warriorlife.net</t>
+          <t>xanthe.delacroix@warriorlife.net</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>9/11/2025 22:19:27</t>
+          <t>9/11/2025 19:54:59</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -2388,32 +2388,32 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Florian</t>
+          <t>Javier</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Rautio</t>
+          <t>Jarvis</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>florian.rautio@warriorlife.net</t>
+          <t>javier.jarvis@warriorlife.net</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>9/12/2025 7:27:01</t>
+          <t>9/12/2025 17:26:37</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -2450,17 +2450,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Fiona</t>
+          <t>Freya</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Silveira</t>
+          <t>Kowalczyk</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>fiona.silveira@warriorlife.net</t>
+          <t>freya.kowalczyk@warriorlife.net</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>9/12/2025 7:58:41</t>
+          <t>9/12/2025 17:29:36</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -2512,58 +2512,58 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Ingrid</t>
+          <t>Teodora</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Zavala</t>
+          <t>Marchetti</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>ingrid.zavala@warriorlife.net</t>
+          <t>zoa.marchetti@warriorlife.net</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>9/12/2025 15:16:47</t>
+          <t>9/12/2025 20:08:31</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ivan</t>
+          <t>Zara</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -2574,32 +2574,32 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Arjun</t>
+          <t>Magnus</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Duran</t>
+          <t>Sibanda</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>arjun.duran@warriorlife.net</t>
+          <t>magnus.sibanda@warriorlife.net</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>9/12/2025 14:43:47</t>
+          <t>9/12/2025 21:17:27</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -2610,12 +2610,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ivan</t>
+          <t>Hina</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Sepulveda</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -2641,12 +2641,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Zola</t>
+          <t>Arjun</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Giordano</t>
+          <t>Duran</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>zola.giordano@warriorlife.net</t>
+          <t>arjun.duran@warriorlife.net</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>9/12/2025 14:43:51</t>
+          <t>9/12/2025 14:43:47</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -2672,12 +2672,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ivan</t>
+          <t>Hina</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Sepulveda</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -2703,34 +2703,30 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Hadley</t>
+          <t>Zola</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Hakim</t>
+          <t>Giordano</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>hadley.hakim@warriorlife.net</t>
+          <t>zola.giordano@warriorlife.net</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>9/12/2025 12:21:40</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>9/12/2025 14:43:51</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2738,12 +2734,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ivan</t>
+          <t>Hina</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Sepulveda</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2753,7 +2749,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -2769,27 +2765,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Yasmin</t>
+          <t>Devika</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Ingersoll</t>
+          <t>Olivares</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>yasmin.ingersoll@warriorlife.net</t>
+          <t>devika.olivares@warriorlife.net</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>9/11/2025 22:14:07</t>
+          <t>9/12/2025 17:54:21</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -2800,12 +2796,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ivan</t>
+          <t>Hina</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Sepulveda</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2815,7 +2811,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -2826,32 +2822,32 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Ahana</t>
+          <t>Theo</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Requena</t>
+          <t>Sathe</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>ahana.vargas@warriorlife.net</t>
+          <t>theo.sathe@warriorlife.net</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>9/12/2025 9:20:27</t>
+          <t>9/13/2025 11:02:16</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -2862,12 +2858,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ivan</t>
+          <t>Hina</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Sepulveda</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2877,7 +2873,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -2888,32 +2884,32 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Shalini</t>
+          <t>Quinn</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Wickham</t>
+          <t>Souza</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>shalini.wickham@warriorlife.net</t>
+          <t>peeira.souza@warriorlife.net</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>9/12/2025 14:13:43</t>
+          <t>9/13/2025 11:03:00</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -2924,12 +2920,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ivan</t>
+          <t>Hina</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Sepulveda</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2939,7 +2935,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -2950,58 +2946,58 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>ravi</t>
+          <t>Vance Avani</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>nkemdirim</t>
+          <t>Souza</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>ravi.nkemdirim@warriorlife.net</t>
+          <t>ct.souza@warriorlife.net</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>9/11/2025 22:16:21</t>
+          <t>9/11/2025 22:55:43</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kavya</t>
+          <t>Hina</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sotelo</t>
+          <t>Sepulveda</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -3012,32 +3008,32 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Beatriz</t>
+          <t>Andre</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Zeidler</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>beatriz.krishnan@warriorlife.net</t>
+          <t>t.zeidler@warriorlife.net</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>9/11/2025 11:50:43</t>
+          <t>9/11/2025 22:55:30</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -3048,22 +3044,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Kavya</t>
+          <t>Ivan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sotelo</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -3074,35 +3070,39 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Hadley</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Mikkelsen</t>
+          <t>Hakim</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>gabriel.mikkelsen@warriorlife.net</t>
+          <t>hadley.hakim@warriorlife.net</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>9/12/2025 22:12:33</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>9/12/2025 12:21:40</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3110,22 +3110,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kavya</t>
+          <t>Ivan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sotelo</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -3136,32 +3136,32 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Noor</t>
+          <t>Yasmin</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Renard</t>
+          <t>Ingersoll</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>noor.renard@warriorlife.net</t>
+          <t>yasmin.ingersoll@warriorlife.net</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>9/12/2025 22:12:36</t>
+          <t>9/11/2025 22:14:07</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -3172,22 +3172,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Kavya</t>
+          <t>Ivan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sotelo</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -3203,12 +3203,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Soren</t>
+          <t>Beatriz</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Rosales</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>soren.rosales@warriorlife.net</t>
+          <t>beatriz.krishnan@warriorlife.net</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>9/12/2025 20:14:49</t>
+          <t>9/11/2025 11:50:43</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -3234,22 +3234,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Kavya</t>
+          <t>Ivan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sotelo</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -3260,32 +3260,32 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Declan</t>
+          <t>Ahana</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Sotelo</t>
+          <t>Requena</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>declan.sotelo@warriorlife.net</t>
+          <t>ahana.vargas@warriorlife.net</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>9/13/2025 8:58:25</t>
+          <t>9/12/2025 9:20:27</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -3296,22 +3296,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Kavya</t>
+          <t>Ivan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sotelo</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -3327,43 +3327,43 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Kavya</t>
+          <t>Declan</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Wahlberg</t>
+          <t>Sotelo</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>kavya.wahlberg@warriorlife.net</t>
+          <t>declan.sotelo@warriorlife.net</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>9/12/2025 16:26:38</t>
+          <t>9/13/2025 8:58:25</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Stellan</t>
+          <t>Ivan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3384,48 +3384,48 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Neel</t>
+          <t>Shalini</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Falconer</t>
+          <t>Wickham</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>neel.falconer@warriorlife.net</t>
+          <t>shalini.wickham@warriorlife.net</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>9/11/2025 23:10:24</t>
+          <t>9/12/2025 14:13:43</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Stellan</t>
+          <t>Ivan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3446,17 +3446,17 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Gia</t>
+          <t>ravi</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Ferraro</t>
+          <t>nkemdirim</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>gia.ferraro@warriorlife.net</t>
+          <t>ravi.nkemdirim@warriorlife.net</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>9/12/2025 22:13:40</t>
+          <t>9/11/2025 22:16:21</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -3482,22 +3482,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Stellan</t>
+          <t>Kavya</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>Sotelo</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Financial Consulting (FCE)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -3508,17 +3508,17 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Ugo</t>
+          <t>Cyrus</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Lundgren</t>
+          <t>Dalmau</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>ugo.lundgren@warriorlife.net</t>
+          <t>cyrus.dalmau@warriorlife.net</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>9/12/2025 15:54:11</t>
+          <t>9/12/2025 12:47:50</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -3544,22 +3544,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Stellan</t>
+          <t>Kavya</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>Sotelo</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Financial Consulting (FCE)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -3570,17 +3570,17 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Mona</t>
+          <t>Mariam</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Montague</t>
+          <t>Mahmood</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>mona.montague@warriorlife.net</t>
+          <t>mariam.mahmood@warriorlife.net</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>9/11/2025 22:08:40</t>
+          <t>9/11/2025 22:15:52</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -3606,22 +3606,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Stellan</t>
+          <t>Kavya</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>Sotelo</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Financial Consulting (FCE)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -3632,32 +3632,32 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Devika</t>
+          <t>Nasir</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Olivares</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>devika.olivares@warriorlife.net</t>
+          <t>nasir.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>9/12/2025 17:54:21</t>
+          <t>9/12/2025 6:12:21</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -3668,22 +3668,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Stellan</t>
+          <t>Kavya</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>Sotelo</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Financial Consulting (FCE)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -3694,32 +3694,32 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Yusuf</t>
+          <t>Sinead</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Reyes</t>
+          <t>Odhiambo</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>yusuf.reyes@warriorlife.net</t>
+          <t>sinead.odhiambo@warriorlife.net</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>9/11/2025 22:00:40</t>
+          <t>9/12/2025 15:12:58</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -3730,22 +3730,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Stellan</t>
+          <t>Kavya</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>Sotelo</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Financial Consulting (FCE)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -3756,17 +3756,17 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Mira</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Shanley</t>
+          <t>Ravindran</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3776,38 +3776,38 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>aurora.rugieroshanley@warriorlife.net</t>
+          <t>mirra.ravindran@warriorlife.net</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>9/12/2025 14:01:19</t>
+          <t>9/9/2025 8:01:17</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>sadie</t>
+          <t>Kavya</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>dahlberg</t>
+          <t>Sotelo</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
+          <t>Financial Consulting (FCE)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -3818,17 +3818,17 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Ainsley</t>
+          <t>Vivienne</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Pandit</t>
+          <t>Zambrano</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>ainsley.pandit@warriorlife.net</t>
+          <t>vivienne.zambrano@warriorlife.net</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>9/12/2025 19:09:11</t>
+          <t>9/12/2025 9:55:11</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -3880,32 +3880,32 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Theo</t>
+          <t>Neel</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Sathe</t>
+          <t>Falconer</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>theo.sathe@warriorlife.net</t>
+          <t>neel.falconer@warriorlife.net</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>9/13/2025 11:02:16</t>
+          <t>9/11/2025 23:10:24</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -3942,17 +3942,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Klara</t>
+          <t>Ugo</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Serrano</t>
+          <t>Lundgren</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>klara.serrano@warriorlife.net</t>
+          <t>ugo.lundgren@warriorlife.net</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>9/12/2025 19:50:55</t>
+          <t>9/12/2025 15:54:11</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -4004,32 +4004,32 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Quinn</t>
+          <t>Yusuf</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Souza</t>
+          <t>Reyes</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>peeira.souza@warriorlife.net</t>
+          <t>yusuf.reyes@warriorlife.net</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>9/13/2025 11:03:00</t>
+          <t>9/11/2025 22:00:40</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -4066,17 +4066,17 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Vance Avani</t>
+          <t>Tavish</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Souza</t>
+          <t>Rivas</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>ct.souza@warriorlife.net</t>
+          <t>tavish.rivas@warriorlife.net</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>9/11/2025 22:55:43</t>
+          <t>9/12/2025 19:47:03</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -4128,39 +4128,35 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Kasper</t>
+          <t>Soren</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Winterbourne</t>
+          <t>Rosales</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>kasper.winterbourne@warriorlife.net</t>
+          <t>soren.rosales@warriorlife.net</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>9/13/2025 7:55:43</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>9/12/2025 20:14:49</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4194,48 +4190,48 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Andre</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Zeidler</t>
+          <t>Shanley</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>t.zeidler@warriorlife.net</t>
+          <t>aurora.rugieroshanley@warriorlife.net</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>9/11/2025 22:55:30</t>
+          <t>9/12/2025 14:01:19</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Lila</t>
+          <t>sadie</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Granados</t>
+          <t>dahlberg</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4245,46 +4241,50 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Business Solutions Project (PMBS)</t>
+          <t>Community Giving Project (PMCG)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Entrepreneurship Events</t>
+          <t>Business Operations Research Events</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Community Giving Project (PMCG)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Valentina</t>
+          <t>Kasper</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Achebe</t>
+          <t>Winterbourne</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>valentina.achebe@warriorlife.net</t>
+          <t>kasper.winterbourne@warriorlife.net</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>9/11/2025 19:46:16</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
+          <t>9/13/2025 7:55:43</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Zelda</t>
+          <t>Uma</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Demir</t>
+          <t>Madrigal</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>zelda.demir@warriorlife.net</t>
+          <t>uma.madrigal@warriorlife.net</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>9/12/2025 12:30:51</t>
+          <t>9/12/2025 16:09:17</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Tomas</t>
+          <t>Idris</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Gagnon</t>
+          <t>Mubarak</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>tomas.gagnon@warriorlife.net</t>
+          <t>idris.mubarak@warriorlife.net</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>9/11/2025 21:57:36</t>
+          <t>9/11/2025 22:50:30</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -4447,12 +4447,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Vera</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Kanellis</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4462,12 +4462,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>vera.kanellis@warriorlife.net</t>
+          <t>ceilialorcan.vargas@warriorlife.net</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>9/12/2025 10:47:36</t>
+          <t>9/12/2025 12:24:12</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -4509,27 +4509,27 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Lachlan</t>
+          <t>Nadia</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Novak</t>
+          <t>Whitlock</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>lachlan.novak@warriorlife.net</t>
+          <t>nadia.whitlock@warriorlife.net</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>9/11/2025 20:29:20</t>
+          <t>9/12/2025 8:11:14</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -4566,35 +4566,39 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Business Solutions Project (PMBS)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Ivo</t>
+          <t>Livia</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Wanjiru</t>
+          <t>Yildirim</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>ivo.wanjiru@warriorlife.net</t>
+          <t>livia.yildirim@warriorlife.net</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>9/12/2025 12:30:38</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
+          <t>9/9/2025 9:09:28</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4628,52 +4632,48 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Business Solutions Project (PMBS)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Livia</t>
+          <t>mateo</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Yildirim</t>
+          <t>sifuentes</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>livia.yildirim@warriorlife.net</t>
+          <t>weilun.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>9/9/2025 9:09:28</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>9/12/2025 12:27:46</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Annika</t>
+          <t>Lila</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>Granados</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Business Solutions Project (PMBS)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -4694,32 +4694,32 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Suri</t>
+          <t>Kamal</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Escobar</t>
+          <t>sorensen</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>suri.escobar@warriorlife.net</t>
+          <t>kamal.sorensen@warriorlife.net</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>9/12/2025 23:28:28</t>
+          <t>9/12/2025 18:30:57</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -4761,12 +4761,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Esteban</t>
+          <t>Davina</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Haddad</t>
+          <t>Avila</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>esteban.haddad@warriorlife.net</t>
+          <t>davina.avila@warriorlife.net</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>9/12/2025 18:44:57</t>
+          <t>9/12/2025 7:55:09</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -4823,27 +4823,27 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Hassan</t>
+          <t>Felicity</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Hollingsworth</t>
+          <t>Avila</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>hassan.hollingsworth@warriorlife.net</t>
+          <t>felicity.avila@warriorlife.net</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>9/12/2025 21:25:44</t>
+          <t>9/12/2025 8:02:01</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -4880,17 +4880,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Celine</t>
+          <t>Oscar</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Wadsworth</t>
+          <t>Draper</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>celine.wadsworth@warriorlife.net</t>
+          <t>oscar.draper@warriorlife.net</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>9/12/2025 14:28:55</t>
+          <t>9/12/2025 12:35:28</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -4947,27 +4947,27 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Aneesha</t>
+          <t>Anders</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Zabala</t>
+          <t>Havili</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>aneesha.zabala@warriorlife.net</t>
+          <t>anders.havili@warriorlife.net</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>9/9/2025 8:54:42</t>
+          <t>9/12/2025 13:38:37</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -5009,12 +5009,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>dashiell</t>
+          <t>Aria</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>imogen</t>
+          <t>Ilyas</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5024,38 +5024,38 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>dashiell.imogen@warriorlife.net</t>
+          <t>aria.ilyas@warriorlife.net</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>9/11/2025 21:37:29</t>
+          <t>9/12/2025 13:40:41</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Edda</t>
+          <t>Annika</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Jensen</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -5066,17 +5066,17 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Fabian</t>
+          <t>Aiden-Bodhi</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Eberhardt</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>v.eberhardt@warriorlife.net</t>
+          <t>aidenbodhi.vargas@warriorlife.net</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>9/11/2025 22:25:02</t>
+          <t>9/12/2025 12:31:44</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -5102,22 +5102,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Edda</t>
+          <t>Tadeo</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Loureiro</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+          <t>Community Giving Project (PMCG)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
@@ -5128,32 +5128,32 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Naila</t>
+          <t>Valentina</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Gagnon</t>
+          <t>Achebe</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>naila.gagnon@warriorlife.net</t>
+          <t>valentina.achebe@warriorlife.net</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>9/10/2025 14:32:40</t>
+          <t>9/11/2025 19:46:16</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -5164,22 +5164,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Edda</t>
+          <t>Tadeo</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Loureiro</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+          <t>Community Giving Project (PMCG)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
@@ -5190,32 +5190,32 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Sienna</t>
+          <t>Zelda</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Demir</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>sienna.moreau@warriorlife.net</t>
+          <t>zelda.demir@warriorlife.net</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>9/12/2025 10:51:31</t>
+          <t>9/12/2025 12:30:51</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -5226,22 +5226,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Edda</t>
+          <t>Tadeo</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Loureiro</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+          <t>Community Giving Project (PMCG)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -5252,35 +5252,39 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Community Giving Project (PMCG)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Fatima</t>
+          <t>Salim</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Redmond</t>
+          <t>Jarrah</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>fatima.redmond@warriorlife.net</t>
+          <t>salim.jarrah@warriorlife.net</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>9/11/2025 21:13:52</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
+          <t>9/12/2025 13:12:11</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5288,22 +5292,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Edda</t>
+          <t>Tadeo</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Loureiro</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+          <t>Community Giving Project (PMCG)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
@@ -5314,17 +5318,17 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Colette</t>
+          <t>Vera</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Reinholt</t>
+          <t>Kanellis</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5334,12 +5338,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>colette.reinholt@warriorlife.net</t>
+          <t>vera.kanellis@warriorlife.net</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>9/11/2025 21:37:33</t>
+          <t>9/12/2025 10:47:36</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -5350,22 +5354,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Edda</t>
+          <t>Tadeo</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Loureiro</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+          <t>Community Giving Project (PMCG)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
@@ -5376,32 +5380,32 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Rhys</t>
+          <t>Lachlan</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>katayama</t>
+          <t>Novak</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>rhys.katayama@warriorlife.net</t>
+          <t>lachlan.novak@warriorlife.net</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>9/10/2025 20:12:09</t>
+          <t>9/11/2025 20:29:20</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -5412,22 +5416,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Edda</t>
+          <t>Tadeo</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Loureiro</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+          <t>Community Giving Project (PMCG)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
@@ -5438,39 +5442,39 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Phoebe</t>
+          <t>Celine</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>sifuentes</t>
+          <t>Wadsworth</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>phebe.sifuentes@warriorlife.net</t>
+          <t>celine.wadsworth@warriorlife.net</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>9/12/2025 10:51:29</t>
+          <t>9/12/2025 14:28:55</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -5479,17 +5483,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Mercado</t>
+          <t>Loureiro</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Community Awareness Project (PMCA)</t>
+          <t>Community Giving Project (PMCG)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
@@ -5500,32 +5504,32 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Carmen</t>
+          <t>Ivo</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Delacroix</t>
+          <t>Wanjiru</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>carmen.delacroix@warriorlife.net</t>
+          <t>ivo.wanjiru@warriorlife.net</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>9/12/2025 17:05:07</t>
+          <t>9/12/2025 12:30:38</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -5562,32 +5566,32 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Eitan</t>
+          <t>Samara</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Lauridsen</t>
+          <t>Bergstrom</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>eitan.lauridsen@warriorlife.net</t>
+          <t>linrui.bergstrom@warriorlife.net</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>9/12/2025 14:11:35</t>
+          <t>9/12/2025 14:01:32</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -5624,32 +5628,32 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Olamide</t>
+          <t>Lena</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Noorani</t>
+          <t>Doyle</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>olamide.noorani@warriorlife.net</t>
+          <t>an.doyle@warriorlife.net</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>9/12/2025 14:12:28</t>
+          <t>9/11/2025 22:13:25</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
@@ -5686,32 +5690,32 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Cassian</t>
+          <t>Suri</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Nuri</t>
+          <t>Escobar</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>cassian.nuri@warriorlife.net</t>
+          <t>suri.escobar@warriorlife.net</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>9/12/2025 14:14:54</t>
+          <t>9/12/2025 23:28:28</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -5748,32 +5752,32 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Manon Nuri</t>
+          <t>Esteban</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Nuri</t>
+          <t>Haddad</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>manon.nuri@warriorlife.net</t>
+          <t>esteban.haddad@warriorlife.net</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>9/12/2025 14:13:11</t>
+          <t>9/12/2025 18:44:57</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -5810,58 +5814,58 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Aarav</t>
+          <t>Hassan</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Ostrowski</t>
+          <t>Hollingsworth</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>d.brannordstrom@warriorlife.net</t>
+          <t>hassan.hollingsworth@warriorlife.net</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>9/12/2025 14:14:36</t>
+          <t>9/12/2025 21:25:44</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Solene</t>
+          <t>Tadeo</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Mercado</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Community Awareness Project (PMCA)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
@@ -5872,58 +5876,58 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Yael</t>
+          <t>Wren</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Caldeira</t>
+          <t>Mikkelsen</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>yael.caldeira@warriorlife.net</t>
+          <t>wren.mikkelsen@warriorlife.net</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>9/11/2025 22:37:04</t>
+          <t>9/12/2025 7:15:29</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Solene</t>
+          <t>Tadeo</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Mercado</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Community Awareness Project (PMCA)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
@@ -5934,17 +5938,17 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Kiran</t>
+          <t>Aneesha</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Chidozie</t>
+          <t>Zabala</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5954,12 +5958,12 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>kiran.chidozie@warriorlife.net</t>
+          <t>aneesha.zabala@warriorlife.net</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>9/11/2025 22:22:21</t>
+          <t>9/9/2025 8:54:42</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
@@ -6001,12 +6005,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Alana</t>
+          <t>Yael</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Cisneros</t>
+          <t>Caldeira</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6016,12 +6020,12 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>lelerc.cisneros@warriorlife.net</t>
+          <t>yael.caldeira@warriorlife.net</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>9/12/2025 21:19:28</t>
+          <t>9/11/2025 22:37:04</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -6063,12 +6067,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Sohan</t>
+          <t>Alana</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Maldonado</t>
+          <t>Cisneros</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6078,12 +6082,12 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>kwanming.maldonado@warriorlife.net</t>
+          <t>lelerc.cisneros@warriorlife.net</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>9/11/2025 22:40:20</t>
+          <t>9/12/2025 21:19:28</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
@@ -6125,27 +6129,27 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Sohan</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Mancini</t>
+          <t>Maldonado</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>camila.mancini@warriorlife.net</t>
+          <t>kwanming.maldonado@warriorlife.net</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>9/11/2025 22:38:14</t>
+          <t>9/11/2025 22:40:20</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
@@ -6249,43 +6253,43 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Vikram</t>
+          <t>Fatima</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Vaidya</t>
+          <t>Redmond</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>vikram.vaidya@warriorlife.net</t>
+          <t>fatima.redmond@warriorlife.net</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>9/11/2025 22:12:43</t>
+          <t>9/11/2025 21:13:52</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Solene</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Obradovic</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6295,7 +6299,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
@@ -6306,48 +6310,48 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Colette</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Dhillon</t>
+          <t>Reinholt</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>renata.dhillon@warriorlife.net</t>
+          <t>colette.reinholt@warriorlife.net</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>9/9/2025 9:47:37</t>
+          <t>9/11/2025 21:37:33</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Solene</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Obradovic</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6357,7 +6361,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
@@ -6368,17 +6372,17 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Athena</t>
+          <t>dashiell</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Dumont</t>
+          <t>imogen</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6388,12 +6392,12 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>athena.dumont@warriorlife.net</t>
+          <t>dashiell.imogen@warriorlife.net</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>9/11/2025 22:34:17</t>
+          <t>9/11/2025 21:37:29</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -6430,32 +6434,32 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Corin</t>
+          <t>Kiran</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Espinoza</t>
+          <t>Chidozie</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>corin.espinoza@warriorlife.net</t>
+          <t>kiran.chidozie@warriorlife.net</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>9/12/2025 7:41:28</t>
+          <t>9/11/2025 22:22:21</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -6492,32 +6496,32 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Rosalind</t>
+          <t>Naila</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Gauthier</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>sinead.gauthier@warriorlife.net</t>
+          <t>naila.gagnon@warriorlife.net</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>9/12/2025 7:28:39</t>
+          <t>9/10/2025 14:32:40</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -6559,27 +6563,27 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Imogen Maeve</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>Mancini</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>maiam.jensen@warriorlife.net</t>
+          <t>camila.mancini@warriorlife.net</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>9/11/2025 23:40:36</t>
+          <t>9/11/2025 22:38:14</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
@@ -6621,27 +6625,27 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Raina</t>
+          <t>Sienna</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Melendez</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>raina.melendez@warriorlife.net</t>
+          <t>sienna.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>9/12/2025 8:41:42</t>
+          <t>9/12/2025 10:51:31</t>
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
@@ -6678,48 +6682,48 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Jarrah</t>
+          <t>Vikram</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Ruggiero</t>
+          <t>Vaidya</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>jarrah.ruggiero@warriorlife.net</t>
+          <t>vikram.vaidya@warriorlife.net</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>9/11/2025 22:00:44</t>
+          <t>9/11/2025 22:12:43</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Darius</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Obradovic</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6740,48 +6744,48 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Indira</t>
+          <t>Rhys</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>katayama</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>indira.andersen@warriorlife.net</t>
+          <t>rhys.katayama@warriorlife.net</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>9/12/2025 14:52:00</t>
+          <t>9/10/2025 20:12:09</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Darius</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Obradovic</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6802,32 +6806,32 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Phoebe</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Beaumont</t>
+          <t>sifuentes</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>gabriel.beaumont@warriorlife.net</t>
+          <t>phebe.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>9/11/2025 22:07:49</t>
+          <t>9/12/2025 10:51:29</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -6838,22 +6842,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Darius</t>
+          <t>Ilana</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
@@ -6864,32 +6868,32 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Nalini</t>
+          <t>Carmen</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Laghari</t>
+          <t>Delacroix</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>nalini.laghari@warriorlife.net</t>
+          <t>carmen.delacroix@warriorlife.net</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>9/11/2025 22:10:45</t>
+          <t>9/12/2025 17:05:07</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
@@ -6900,22 +6904,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Darius</t>
+          <t>Ilana</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
@@ -6926,32 +6930,32 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Wren</t>
+          <t>Eitan</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Mikkelsen</t>
+          <t>Lauridsen</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>wren.mikkelsen@warriorlife.net</t>
+          <t>eitan.lauridsen@warriorlife.net</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>9/12/2025 7:15:29</t>
+          <t>9/12/2025 14:11:35</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
@@ -6962,22 +6966,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Darius</t>
+          <t>Ilana</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
@@ -6988,17 +6992,17 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Jian</t>
+          <t>Olamide</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Noorani</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -7008,12 +7012,12 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>jian.moreau@warriorlife.net</t>
+          <t>olamide.noorani@warriorlife.net</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>9/11/2025 22:12:23</t>
+          <t>9/12/2025 14:12:28</t>
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
@@ -7024,22 +7028,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Darius</t>
+          <t>Ilana</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
@@ -7050,17 +7054,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Ramona</t>
+          <t>Cassian</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Nascimento</t>
+          <t>Nuri</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7070,12 +7074,12 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>ramona.nascimento@warriorlife.net</t>
+          <t>cassian.nuri@warriorlife.net</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>9/12/2025 7:53:24</t>
+          <t>9/12/2025 14:14:54</t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
@@ -7086,22 +7090,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Darius</t>
+          <t>Ilana</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
@@ -7112,48 +7116,48 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Nils</t>
+          <t>Manon Nuri</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Vasquez</t>
+          <t>Nuri</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>nils.vasquez@warriorlife.net</t>
+          <t>manon.nuri@warriorlife.net</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>9/12/2025 7:55:43</t>
+          <t>9/12/2025 14:13:11</t>
         </is>
       </c>
       <c r="N108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Hina</t>
+          <t>Ilana</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Sepulveda</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7163,7 +7167,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
@@ -7179,27 +7183,27 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Kian</t>
+          <t>Aarav</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Guerrero</t>
+          <t>Ostrowski</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>kian.guerrero@warriorlife.net</t>
+          <t>d.brannordstrom@warriorlife.net</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>9/12/2025 10:58:13</t>
+          <t>9/12/2025 14:14:36</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
@@ -7210,22 +7214,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Hina</t>
+          <t>Darius</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Sepulveda</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
@@ -7236,32 +7240,32 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Lorcan</t>
+          <t>Athena</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Milburn</t>
+          <t>Dumont</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>lorcan.milburn@warriorlife.net</t>
+          <t>athena.dumont@warriorlife.net</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>9/12/2025 21:17:34</t>
+          <t>9/11/2025 22:34:17</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -7272,22 +7276,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Hina</t>
+          <t>Darius</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Sepulveda</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
@@ -7298,17 +7302,17 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Senna</t>
+          <t>Fabian</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Petrov</t>
+          <t>Eberhardt</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -7318,12 +7322,12 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>senna.petrov@warriorlife.net</t>
+          <t>v.eberhardt@warriorlife.net</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>9/12/2025 10:47:55</t>
+          <t>9/11/2025 22:25:02</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -7334,22 +7338,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Hina</t>
+          <t>Darius</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Sepulveda</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
@@ -7365,27 +7369,27 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Alec</t>
+          <t>Rosalind</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Sheridan</t>
+          <t>Gauthier</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>alec.sheridan@warriorlife.net</t>
+          <t>sinead.gauthier@warriorlife.net</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>9/12/2025 23:14:55</t>
+          <t>9/12/2025 7:28:39</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -7396,22 +7400,22 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Hina</t>
+          <t>Darius</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Sepulveda</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
@@ -7422,32 +7426,32 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Zelda</t>
+          <t>Imogen Maeve</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Tiwari</t>
+          <t>Jensen</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>zelda.tiwari@warriorlife.net</t>
+          <t>maiam.jensen@warriorlife.net</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>9/12/2025 21:53:17</t>
+          <t>9/11/2025 23:40:36</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -7458,22 +7462,22 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Hina</t>
+          <t>Darius</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Sepulveda</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
@@ -7484,17 +7488,17 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Lian</t>
+          <t>Raina</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Zoric</t>
+          <t>Melendez</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -7504,38 +7508,38 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>lian.zoric@warriorlife.net</t>
+          <t>raina.melendez@warriorlife.net</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>9/12/2025 16:44:11</t>
+          <t>9/12/2025 8:41:42</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Nova</t>
+          <t>Darius</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Stanek</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
@@ -7546,58 +7550,58 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Jarrah</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Bergstrom</t>
+          <t>Ruggiero</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>linrui.bergstrom@warriorlife.net</t>
+          <t>jarrah.ruggiero@warriorlife.net</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>9/12/2025 14:01:32</t>
+          <t>9/11/2025 22:00:44</t>
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Nova</t>
+          <t>Darius</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Stanek</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
@@ -7608,17 +7612,17 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Lena</t>
+          <t>Zelda</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Doyle</t>
+          <t>Tiwari</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7628,12 +7632,12 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>an.doyle@warriorlife.net</t>
+          <t>zelda.tiwari@warriorlife.net</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>9/11/2025 22:13:25</t>
+          <t>9/12/2025 21:53:17</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -7670,32 +7674,32 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Nara</t>
+          <t>Tomas</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Garrido</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>nara.garrido@warriorlife.net</t>
+          <t>tomas.gagnon@warriorlife.net</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>9/11/2025 22:28:55</t>
+          <t>9/11/2025 21:57:36</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -7732,39 +7736,35 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Tuan</t>
+          <t>Nara</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Hartley</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>tuan.hartley@warriorlife.net</t>
+          <t>nara.garrido@warriorlife.net</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>9/10/2025 15:40:55</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>9/11/2025 22:28:55</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -7798,35 +7798,39 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Theo</t>
+          <t>Tuan</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Herrera</t>
+          <t>Hartley</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>theo.herrera@warriorlife.net</t>
+          <t>tuan.hartley@warriorlife.net</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>9/12/2025 10:59:12</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
+          <t>9/10/2025 15:40:55</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7860,39 +7864,35 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Harlow</t>
+          <t>Theo</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Savage</t>
+          <t>Herrera</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>harlow.savage@warriorlife.net</t>
+          <t>theo.herrera@warriorlife.net</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>9/12/2025 13:10:47</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>9/12/2025 10:59:12</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7926,48 +7926,48 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Imani</t>
+          <t>Eamon</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Kasprzak</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>manus.sifuentes@warriorlife.net</t>
+          <t>eamon.kasprzak@warriorlife.net</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>9/11/2025 21:55:46</t>
+          <t>9/13/2025 6:42:32</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>astrid</t>
+          <t>Nova</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>kaufman</t>
+          <t>Stanek</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
@@ -7988,17 +7988,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Eamon</t>
+          <t>Harlow</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Kasprzak</t>
+          <t>Savage</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -8008,28 +8008,32 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>eamon.kasprzak@warriorlife.net</t>
+          <t>harlow.savage@warriorlife.net</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>9/13/2025 6:42:32</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr"/>
+          <t>9/12/2025 13:10:47</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>astrid</t>
+          <t>Nova</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>kaufman</t>
+          <t>Stanek</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -8039,7 +8043,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="F123" t="inlineStr"/>
@@ -8050,17 +8054,17 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Uma</t>
+          <t>Imani</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Madrigal</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8070,12 +8074,12 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>uma.madrigal@warriorlife.net</t>
+          <t>manus.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>9/12/2025 16:09:17</t>
+          <t>9/11/2025 21:55:46</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
@@ -8086,22 +8090,22 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>astrid</t>
+          <t>Hazel</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>kaufman</t>
+          <t>Svensson</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
@@ -8112,32 +8116,32 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Idris</t>
+          <t>Indira</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Mubarak</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>idris.mubarak@warriorlife.net</t>
+          <t>indira.andersen@warriorlife.net</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>9/11/2025 22:50:30</t>
+          <t>9/12/2025 14:52:00</t>
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
@@ -8148,22 +8152,22 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>astrid</t>
+          <t>Hazel</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>kaufman</t>
+          <t>Svensson</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
@@ -8174,17 +8178,17 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>Beaumont</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -8194,12 +8198,12 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>ceilialorcan.vargas@warriorlife.net</t>
+          <t>gabriel.beaumont@warriorlife.net</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>9/12/2025 12:24:12</t>
+          <t>9/11/2025 22:07:49</t>
         </is>
       </c>
       <c r="N125" t="inlineStr"/>
@@ -8210,22 +8214,22 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>astrid</t>
+          <t>Hazel</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>kaufman</t>
+          <t>Svensson</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
@@ -8236,17 +8240,17 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Nadia</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Whitlock</t>
+          <t>Dhillon</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -8256,12 +8260,12 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>nadia.whitlock@warriorlife.net</t>
+          <t>renata.dhillon@warriorlife.net</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>9/12/2025 8:11:14</t>
+          <t>9/9/2025 9:47:37</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
@@ -8272,22 +8276,22 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>astrid</t>
+          <t>Hazel</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>kaufman</t>
+          <t>Svensson</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="F127" t="inlineStr"/>
@@ -8298,17 +8302,17 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>mateo</t>
+          <t>Nalini</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>sifuentes</t>
+          <t>Laghari</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -8318,12 +8322,12 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>weilun.sifuentes@warriorlife.net</t>
+          <t>nalini.laghari@warriorlife.net</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>9/12/2025 12:27:46</t>
+          <t>9/11/2025 22:10:45</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
@@ -8334,22 +8338,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>astrid</t>
+          <t>Hazel</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>kaufman</t>
+          <t>Svensson</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="F128" t="inlineStr"/>
@@ -8360,48 +8364,48 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Kamal</t>
+          <t>Jian</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>sorensen</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>kamal.sorensen@warriorlife.net</t>
+          <t>jian.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>9/12/2025 18:30:57</t>
+          <t>9/11/2025 22:12:23</t>
         </is>
       </c>
       <c r="N128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>delphine</t>
+          <t>Hazel</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>zabala</t>
+          <t>Svensson</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8411,7 +8415,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
@@ -8427,12 +8431,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Davina</t>
+          <t>Ramona</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Avila</t>
+          <t>Nascimento</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -8442,28 +8446,28 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>davina.avila@warriorlife.net</t>
+          <t>ramona.nascimento@warriorlife.net</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>9/12/2025 7:55:09</t>
+          <t>9/12/2025 7:53:24</t>
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>delphine</t>
+          <t>Hazel</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>zabala</t>
+          <t>Svensson</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -8473,7 +8477,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
@@ -8489,12 +8493,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Felicity</t>
+          <t>Nils</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Avila</t>
+          <t>Vasquez</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -8504,12 +8508,12 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>felicity.avila@warriorlife.net</t>
+          <t>nils.vasquez@warriorlife.net</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>9/12/2025 8:02:01</t>
+          <t>9/12/2025 7:55:43</t>
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
@@ -8520,22 +8524,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>delphine</t>
+          <t>astrid</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>zabala</t>
+          <t>kaufman</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
@@ -8546,32 +8550,32 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Oscar</t>
+          <t>Corin</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Draper</t>
+          <t>Espinoza</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>oscar.draper@warriorlife.net</t>
+          <t>corin.espinoza@warriorlife.net</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>9/12/2025 12:35:28</t>
+          <t>9/12/2025 7:41:28</t>
         </is>
       </c>
       <c r="N131" t="inlineStr"/>
@@ -8582,22 +8586,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>delphine</t>
+          <t>astrid</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>zabala</t>
+          <t>kaufman</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
@@ -8608,32 +8612,32 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Anders</t>
+          <t>Kian</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Havili</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>anders.havili@warriorlife.net</t>
+          <t>kian.guerrero@warriorlife.net</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>9/12/2025 13:38:37</t>
+          <t>9/12/2025 10:58:13</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -8644,22 +8648,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>delphine</t>
+          <t>astrid</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>zabala</t>
+          <t>kaufman</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="F133" t="inlineStr"/>
@@ -8670,32 +8674,32 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Aria</t>
+          <t>Lorcan</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Ilyas</t>
+          <t>Milburn</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>aria.ilyas@warriorlife.net</t>
+          <t>lorcan.milburn@warriorlife.net</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>9/12/2025 13:40:41</t>
+          <t>9/12/2025 21:17:34</t>
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
@@ -8706,22 +8710,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>delphine</t>
+          <t>astrid</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>zabala</t>
+          <t>kaufman</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="F134" t="inlineStr"/>
@@ -8732,17 +8736,17 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Aiden-Bodhi</t>
+          <t>Senna</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>Petrov</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8752,136 +8756,136 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>aidenbodhi.vargas@warriorlife.net</t>
+          <t>senna.petrov@warriorlife.net</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>9/12/2025 12:31:44</t>
+          <t>9/12/2025 10:47:55</t>
         </is>
       </c>
       <c r="N134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Tadeo</t>
+          <t>astrid</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Loureiro</t>
+          <t>kaufman</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign Events</t>
+          <t>Entrepreneurship Events</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Event (IMCE)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Anika</t>
+          <t>Alec</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Alvarez</t>
+          <t>Sheridan</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>sk.alvarez@warriorlife.net</t>
+          <t>alec.sheridan@warriorlife.net</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>9/12/2025 8:00:43</t>
+          <t>9/12/2025 23:14:55</t>
         </is>
       </c>
       <c r="N135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Tadeo</t>
+          <t>astrid</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Loureiro</t>
+          <t>kaufman</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign Events</t>
+          <t>Entrepreneurship Events</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Event (IMCE)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Shai</t>
+          <t>Lian</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Darrow</t>
+          <t>Zoric</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>shai.darrow@warriorlife.net</t>
+          <t>lian.zoric@warriorlife.net</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>9/12/2025 0:58:27</t>
+          <t>9/12/2025 16:44:11</t>
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
@@ -8892,22 +8896,22 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Tadeo</t>
+          <t>Edda</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Loureiro</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
+          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
@@ -8918,32 +8922,32 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Event (IMCE)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Kenji</t>
+          <t>Tarek</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Herrera</t>
+          <t>Adeyemi</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>kenji.herrera@warriorlife.net</t>
+          <t>tarek.adeyemi@warriorlife.net</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>9/12/2025 21:59:50</t>
+          <t>9/12/2025 15:14:00</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
@@ -8954,22 +8958,22 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Tadeo</t>
+          <t>Edda</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Loureiro</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
+          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
@@ -8980,17 +8984,17 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Salim</t>
+          <t>Svea</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Jarrah</t>
+          <t>Brandt</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -9000,19 +9004,15 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>salim.jarrah@warriorlife.net</t>
+          <t>svea.brandt@warriorlife.net</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>9/12/2025 13:12:11</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>9/12/2025 23:13:38</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Tadeo</t>
+          <t>Edda</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Loureiro</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
+          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
@@ -9046,32 +9046,32 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Event (IMCE)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Lyra</t>
+          <t>Diya</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Katayama</t>
+          <t>Fitzgerald</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>lyra.katayama@warriorlife.net</t>
+          <t>diya.fitzgerald@warriorlife.net</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>9/12/2025 8:00:27</t>
+          <t>9/13/2025 14:58:43</t>
         </is>
       </c>
       <c r="N139" t="inlineStr"/>
@@ -9082,22 +9082,22 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Tadeo</t>
+          <t>Edda</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Loureiro</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
+          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
@@ -9108,17 +9108,17 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Anton</t>
+          <t>Chandra</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Mbeki</t>
+          <t>Fonseca</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -9128,38 +9128,38 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>anton.mbeki@warriorlife.net</t>
+          <t>chandra.fonseca@warriorlife.net</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>9/10/2025 14:35:18</t>
+          <t>9/11/2025 22:14:39</t>
         </is>
       </c>
       <c r="N140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Ilana</t>
+          <t>Edda</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
@@ -9175,53 +9175,53 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Tarek</t>
+          <t>Elara</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Adeyemi</t>
+          <t>Mehrotra</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>tarek.adeyemi@warriorlife.net</t>
+          <t>elara.mehrotra@warriorlife.net</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>9/12/2025 15:14:00</t>
+          <t>9/12/2025 22:08:36</t>
         </is>
       </c>
       <c r="N141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Ilana</t>
+          <t>Edda</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
         </is>
       </c>
       <c r="F142" t="inlineStr"/>
@@ -9237,27 +9237,27 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Malia</t>
+          <t>Ayaan</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Villanueva</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>malia.andersen@warriorlife.net</t>
+          <t>ayaan.villanueva@warriorlife.net</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>9/12/2025 15:02:39</t>
+          <t>9/12/2025 15:04:57</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
@@ -9268,12 +9268,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Ilana</t>
+          <t>Stellan</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -9283,7 +9283,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="F143" t="inlineStr"/>
@@ -9294,32 +9294,32 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Svea</t>
+          <t>Yara</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Brandt</t>
+          <t>Gundersen</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>svea.brandt@warriorlife.net</t>
+          <t>yara.gundersen@warriorlife.net</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>9/12/2025 23:13:38</t>
+          <t>9/12/2025 16:54:05</t>
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
@@ -9330,12 +9330,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ilana</t>
+          <t>Stellan</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -9345,7 +9345,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="F144" t="inlineStr"/>
@@ -9356,32 +9356,32 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Chiara</t>
+          <t>Anton</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Callahan</t>
+          <t>Mbeki</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>chiara.callahan@warriorlife.net</t>
+          <t>anton.mbeki@warriorlife.net</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>9/12/2025 7:45:09</t>
+          <t>9/10/2025 14:35:18</t>
         </is>
       </c>
       <c r="N144" t="inlineStr"/>
@@ -9392,12 +9392,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Ilana</t>
+          <t>Stellan</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
@@ -9418,32 +9418,32 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Chandra</t>
+          <t>Emeka</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Fonseca</t>
+          <t>Nascimento</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>chandra.fonseca@warriorlife.net</t>
+          <t>emeka.nascimento@warriorlife.net</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>9/11/2025 22:14:39</t>
+          <t>9/12/2025 17:12:18</t>
         </is>
       </c>
       <c r="N145" t="inlineStr"/>
@@ -9454,12 +9454,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Ilana</t>
+          <t>Stellan</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9469,7 +9469,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="F146" t="inlineStr"/>
@@ -9480,17 +9480,17 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Elara</t>
+          <t>Eero</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Mehrotra</t>
+          <t>Rothman</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -9500,12 +9500,12 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>elara.mehrotra@warriorlife.net</t>
+          <t>eero.rothman@warriorlife.net</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>9/12/2025 22:08:36</t>
+          <t>9/12/2025 17:30:29</t>
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
@@ -9516,12 +9516,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Ilana</t>
+          <t>Stellan</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="F147" t="inlineStr"/>
@@ -9542,58 +9542,58 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Ayaan</t>
+          <t>Kavya</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Villanueva</t>
+          <t>Wahlberg</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>ayaan.villanueva@warriorlife.net</t>
+          <t>kavya.wahlberg@warriorlife.net</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>9/12/2025 15:04:57</t>
+          <t>9/12/2025 16:26:38</t>
         </is>
       </c>
       <c r="N147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Hazel</t>
+          <t>Stellan</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Svensson</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>4th Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="F148" t="inlineStr"/>
@@ -9609,12 +9609,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Diya</t>
+          <t>ameer</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Fitzgerald</t>
+          <t>bosco</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>diya.fitzgerald@warriorlife.net</t>
+          <t>ameer.bosco@warriorlife.net</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>9/13/2025 14:58:43</t>
+          <t>9/12/2025 16:54:02</t>
         </is>
       </c>
       <c r="N148" t="inlineStr"/>
@@ -9640,12 +9640,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Hazel</t>
+          <t>delphine</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Svensson</t>
+          <t>zabala</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -9655,7 +9655,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
@@ -9666,32 +9666,32 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Integrated Marketing Campaign - Event (IMCE)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Marco</t>
+          <t>Anika</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Greenway</t>
+          <t>Alvarez</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>3rd Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>marco.greenway@warriorlife.net</t>
+          <t>sk.alvarez@warriorlife.net</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>9/12/2025 16:43:28</t>
+          <t>9/12/2025 8:00:43</t>
         </is>
       </c>
       <c r="N149" t="inlineStr"/>
@@ -9702,12 +9702,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Hazel</t>
+          <t>delphine</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Svensson</t>
+          <t>zabala</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="F150" t="inlineStr"/>
@@ -9728,32 +9728,32 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Emeka</t>
+          <t>Malia</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Nascimento</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>1st Year</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>emeka.nascimento@warriorlife.net</t>
+          <t>malia.andersen@warriorlife.net</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>9/12/2025 17:12:18</t>
+          <t>9/12/2025 15:02:39</t>
         </is>
       </c>
       <c r="N150" t="inlineStr"/>
@@ -9764,12 +9764,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Hazel</t>
+          <t>delphine</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Svensson</t>
+          <t>zabala</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
@@ -9790,32 +9790,32 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Tavish</t>
+          <t>Chiara</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Rivas</t>
+          <t>Callahan</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>2nd Year</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>tavish.rivas@warriorlife.net</t>
+          <t>chiara.callahan@warriorlife.net</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>9/12/2025 19:47:03</t>
+          <t>9/12/2025 7:45:09</t>
         </is>
       </c>
       <c r="N151" t="inlineStr"/>
@@ -9826,12 +9826,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Hazel</t>
+          <t>delphine</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Svensson</t>
+          <t>zabala</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
@@ -9852,32 +9852,32 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Integrated Marketing Campaign - Event (IMCE)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Eero</t>
+          <t>Shai</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Rothman</t>
+          <t>Darrow</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>eero.rothman@warriorlife.net</t>
+          <t>shai.darrow@warriorlife.net</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>9/12/2025 17:30:29</t>
+          <t>9/12/2025 0:58:27</t>
         </is>
       </c>
       <c r="N152" t="inlineStr"/>
@@ -9888,12 +9888,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Hazel</t>
+          <t>delphine</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Svensson</t>
+          <t>zabala</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -9903,7 +9903,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
@@ -9914,58 +9914,58 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Integrated Marketing Campaign - Event (IMCE)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Ashwin</t>
+          <t>Kenji</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Trevino</t>
+          <t>Herrera</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>ashwin.trevino@warriorlife.net</t>
+          <t>kenji.herrera@warriorlife.net</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>9/11/2025 23:54:24</t>
+          <t>9/12/2025 21:59:50</t>
         </is>
       </c>
       <c r="N153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>siri</t>
+          <t>delphine</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>zhelezny</t>
+          <t>zabala</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2nd Year</t>
+          <t>4th Year</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
@@ -9976,32 +9976,32 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Integrated Marketing Campaign - Event (IMCE)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Lyra</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Achebe</t>
+          <t>Katayama</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>1st Year</t>
+          <t>3rd Year</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>gemma.achebe@warriorlife.net</t>
+          <t>lyra.katayama@warriorlife.net</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>9/12/2025 15:56:03</t>
+          <t>9/12/2025 8:00:27</t>
         </is>
       </c>
       <c r="N154" t="inlineStr"/>
@@ -10038,17 +10038,17 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Kabir</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Bakke</t>
+          <t>Achebe</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -10058,19 +10058,15 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>s.bakke@warriorlife.net</t>
+          <t>gemma.achebe@warriorlife.net</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>9/13/2025 0:03:52</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>9/12/2025 15:56:03</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -10104,17 +10100,17 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Yara</t>
+          <t>Kabir</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Gundersen</t>
+          <t>Bakke</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -10124,15 +10120,19 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>yara.gundersen@warriorlife.net</t>
+          <t>s.bakke@warriorlife.net</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>9/12/2025 16:54:05</t>
-        </is>
-      </c>
-      <c r="N156" t="inlineStr"/>
+          <t>9/13/2025 0:03:52</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -10361,12 +10361,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>ameer</t>
+          <t>Ashwin</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>bosco</t>
+          <t>Trevino</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -10376,12 +10376,12 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>ameer.bosco@warriorlife.net</t>
+          <t>ashwin.trevino@warriorlife.net</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>9/12/2025 16:54:02</t>
+          <t>9/11/2025 23:54:24</t>
         </is>
       </c>
       <c r="N160" t="inlineStr"/>
